--- a/simulator/data_bank.xlsx
+++ b/simulator/data_bank.xlsx
@@ -529,31 +529,31 @@
         <v>117</v>
       </c>
       <c r="I2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>1.71</v>
+        <v>0.85</v>
       </c>
       <c r="M2">
         <v>117</v>
       </c>
       <c r="N2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="O2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P2">
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>1.71</v>
+        <v>0.85</v>
       </c>
       <c r="R2">
         <v>9.75</v>
@@ -565,16 +565,16 @@
         <v>-0.25</v>
       </c>
       <c r="U2">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="V2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W2">
-        <v>96.67</v>
+        <v>95</v>
       </c>
       <c r="X2">
-        <v>96.67</v>
+        <v>95</v>
       </c>
       <c r="Y2" t="str">
         <v/>
@@ -603,55 +603,55 @@
         <v>1000</v>
       </c>
       <c r="H3">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I3">
         <v>97</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="M3">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="N3">
         <v>97</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P3">
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="R3">
-        <v>9.7</v>
+        <v>9.8</v>
       </c>
       <c r="S3">
         <v>10</v>
       </c>
       <c r="T3">
-        <v>-0.3</v>
+        <v>-0.2</v>
       </c>
       <c r="U3">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="V3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W3">
-        <v>93.33</v>
+        <v>100</v>
       </c>
       <c r="X3">
-        <v>93.33</v>
+        <v>100</v>
       </c>
       <c r="Y3" t="str">
         <v/>
@@ -680,43 +680,43 @@
         <v>800</v>
       </c>
       <c r="H4">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="I4">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="M4">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="N4">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="O4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4">
         <v>0</v>
       </c>
       <c r="Q4">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="R4">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="S4">
         <v>10</v>
       </c>
       <c r="T4">
-        <v>-0.5</v>
+        <v>-1.5</v>
       </c>
       <c r="U4">
         <v>52</v>
@@ -757,10 +757,10 @@
         <v>750</v>
       </c>
       <c r="H5">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="I5">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -769,13 +769,13 @@
         <v>0</v>
       </c>
       <c r="L5">
-        <v>1.49</v>
+        <v>1.33</v>
       </c>
       <c r="M5">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="N5">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="O5">
         <v>1</v>
@@ -784,28 +784,28 @@
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>1.49</v>
+        <v>1.33</v>
       </c>
       <c r="R5">
-        <v>8.93</v>
+        <v>10</v>
       </c>
       <c r="S5">
         <v>10</v>
       </c>
       <c r="T5">
-        <v>-1.07</v>
+        <v>0</v>
       </c>
       <c r="U5">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="V5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="W5">
-        <v>83.33</v>
+        <v>100</v>
       </c>
       <c r="X5">
-        <v>83.33</v>
+        <v>100</v>
       </c>
       <c r="Y5" t="str">
         <v/>
@@ -834,55 +834,55 @@
         <v>600</v>
       </c>
       <c r="H6">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="I6">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K6">
         <v>0</v>
       </c>
       <c r="L6">
-        <v>1.61</v>
+        <v>3.45</v>
       </c>
       <c r="M6">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="N6">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="O6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P6">
         <v>0</v>
       </c>
       <c r="Q6">
-        <v>1.61</v>
+        <v>3.45</v>
       </c>
       <c r="R6">
-        <v>10.33</v>
+        <v>9.67</v>
       </c>
       <c r="S6">
         <v>10</v>
       </c>
       <c r="T6">
-        <v>0.33</v>
+        <v>-0.33</v>
       </c>
       <c r="U6">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W6">
-        <v>100</v>
+        <v>88.33</v>
       </c>
       <c r="X6">
-        <v>100</v>
+        <v>88.33</v>
       </c>
       <c r="Y6" t="str">
         <v/>
@@ -911,55 +911,55 @@
         <v>550</v>
       </c>
       <c r="H7">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I7">
+        <v>46</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>2.13</v>
+      </c>
+      <c r="M7">
         <v>47</v>
       </c>
-      <c r="J7">
-        <v>2</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-      <c r="L7">
-        <v>4.08</v>
-      </c>
-      <c r="M7">
-        <v>49</v>
-      </c>
       <c r="N7">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P7">
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>4.08</v>
+        <v>2.13</v>
       </c>
       <c r="R7">
-        <v>8.91</v>
+        <v>8.55</v>
       </c>
       <c r="S7">
         <v>10</v>
       </c>
       <c r="T7">
-        <v>-1.09</v>
+        <v>-1.45</v>
       </c>
       <c r="U7">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="V7">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="W7">
-        <v>85</v>
+        <v>93.33</v>
       </c>
       <c r="X7">
-        <v>85</v>
+        <v>93.33</v>
       </c>
       <c r="Y7" t="str">
         <v/>
@@ -991,31 +991,31 @@
         <v>88</v>
       </c>
       <c r="I8">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="J8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K8">
         <v>0</v>
       </c>
       <c r="L8">
-        <v>1.14</v>
+        <v>3.41</v>
       </c>
       <c r="M8">
         <v>88</v>
       </c>
       <c r="N8">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="O8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P8">
         <v>0</v>
       </c>
       <c r="Q8">
-        <v>1.14</v>
+        <v>3.41</v>
       </c>
       <c r="R8">
         <v>9.78</v>
@@ -1027,16 +1027,16 @@
         <v>-0.22</v>
       </c>
       <c r="U8">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="V8">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="W8">
-        <v>88.33</v>
+        <v>93.33</v>
       </c>
       <c r="X8">
-        <v>88.33</v>
+        <v>93.33</v>
       </c>
       <c r="Y8" t="str">
         <v/>
@@ -1065,10 +1065,10 @@
         <v>1500</v>
       </c>
       <c r="H9">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="I9">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -1077,13 +1077,13 @@
         <v>0</v>
       </c>
       <c r="L9">
-        <v>0.68</v>
+        <v>0.69</v>
       </c>
       <c r="M9">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="N9">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="O9">
         <v>1</v>
@@ -1092,28 +1092,28 @@
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>0.68</v>
+        <v>0.69</v>
       </c>
       <c r="R9">
-        <v>9.73</v>
+        <v>9.6</v>
       </c>
       <c r="S9">
         <v>10</v>
       </c>
       <c r="T9">
-        <v>-0.27</v>
+        <v>-0.4</v>
       </c>
       <c r="U9">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="V9">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="W9">
-        <v>98.33</v>
+        <v>88.33</v>
       </c>
       <c r="X9">
-        <v>98.33</v>
+        <v>88.33</v>
       </c>
       <c r="Y9" t="str">
         <v/>
@@ -1142,10 +1142,10 @@
         <v>1400</v>
       </c>
       <c r="H10">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="I10">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -1157,10 +1157,10 @@
         <v>0</v>
       </c>
       <c r="M10">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="N10">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="O10">
         <v>0</v>
@@ -1172,25 +1172,25 @@
         <v>0</v>
       </c>
       <c r="R10">
-        <v>8.57</v>
+        <v>9.21</v>
       </c>
       <c r="S10">
         <v>10</v>
       </c>
       <c r="T10">
-        <v>-1.43</v>
+        <v>-0.79</v>
       </c>
       <c r="U10">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="V10">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W10">
-        <v>83.33</v>
+        <v>90</v>
       </c>
       <c r="X10">
-        <v>83.33</v>
+        <v>90</v>
       </c>
       <c r="Y10" t="str">
         <v/>
@@ -1219,55 +1219,55 @@
         <v>450</v>
       </c>
       <c r="H11">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="I11">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11">
         <v>0</v>
       </c>
       <c r="L11">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="M11">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="N11">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P11">
         <v>0</v>
       </c>
       <c r="Q11">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="R11">
-        <v>8.67</v>
+        <v>9.56</v>
       </c>
       <c r="S11">
         <v>10</v>
       </c>
       <c r="T11">
-        <v>-1.33</v>
+        <v>-0.44</v>
       </c>
       <c r="U11">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="V11">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W11">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="X11">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="Y11" t="str">
         <v/>
@@ -1296,55 +1296,55 @@
         <v>400</v>
       </c>
       <c r="H12">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I12">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12">
         <v>0</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="M12">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="N12">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P12">
         <v>0</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="R12">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="S12">
         <v>10</v>
       </c>
       <c r="T12">
-        <v>-0.5</v>
+        <v>-1</v>
       </c>
       <c r="U12">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="V12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W12">
-        <v>93.33</v>
+        <v>95</v>
       </c>
       <c r="X12">
-        <v>93.33</v>
+        <v>95</v>
       </c>
       <c r="Y12" t="str">
         <v/>
@@ -1373,10 +1373,10 @@
         <v>2000</v>
       </c>
       <c r="H13">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="I13">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="J13">
         <v>1</v>
@@ -1385,13 +1385,13 @@
         <v>0</v>
       </c>
       <c r="L13">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="M13">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="N13">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="O13">
         <v>1</v>
@@ -1400,28 +1400,28 @@
         <v>0</v>
       </c>
       <c r="Q13">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="R13">
-        <v>8.65</v>
+        <v>9.05</v>
       </c>
       <c r="S13">
         <v>10</v>
       </c>
       <c r="T13">
-        <v>-1.35</v>
+        <v>-0.95</v>
       </c>
       <c r="U13">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="V13">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="W13">
-        <v>91.67</v>
+        <v>83.33</v>
       </c>
       <c r="X13">
-        <v>91.67</v>
+        <v>83.33</v>
       </c>
       <c r="Y13" t="str">
         <v/>
@@ -1450,10 +1450,10 @@
         <v>1200</v>
       </c>
       <c r="H14">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="I14">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -1465,37 +1465,37 @@
         <v>0</v>
       </c>
       <c r="M14">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="N14">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="O14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P14">
         <v>0</v>
       </c>
       <c r="Q14">
-        <v>0.83</v>
+        <v>0.42</v>
       </c>
       <c r="R14">
-        <v>20.17</v>
+        <v>19.83</v>
       </c>
       <c r="S14">
         <v>20</v>
       </c>
       <c r="T14">
-        <v>0.17</v>
+        <v>-0.17</v>
       </c>
       <c r="U14">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="V14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W14">
-        <v>98.33</v>
+        <v>100</v>
       </c>
       <c r="X14">
         <v>97.5</v>
@@ -1527,55 +1527,55 @@
         <v>1000</v>
       </c>
       <c r="H15">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I15">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="J15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K15">
         <v>0</v>
       </c>
       <c r="L15">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M15">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="N15">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="O15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P15">
         <v>0</v>
       </c>
       <c r="Q15">
-        <v>1.08</v>
+        <v>0.51</v>
       </c>
       <c r="R15">
-        <v>18.6</v>
+        <v>19.5</v>
       </c>
       <c r="S15">
         <v>20</v>
       </c>
       <c r="T15">
-        <v>-1.4</v>
+        <v>-0.5</v>
       </c>
       <c r="U15">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="V15">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="W15">
-        <v>86.67</v>
+        <v>96.67</v>
       </c>
       <c r="X15">
-        <v>90</v>
+        <v>98.33</v>
       </c>
       <c r="Y15" t="str">
         <v/>
@@ -1604,25 +1604,25 @@
         <v>800</v>
       </c>
       <c r="H16">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="I16">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16">
         <v>0</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M16">
-        <v>158</v>
+        <v>137</v>
       </c>
       <c r="N16">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="O16">
         <v>1</v>
@@ -1631,28 +1631,28 @@
         <v>0</v>
       </c>
       <c r="Q16">
-        <v>0.63</v>
+        <v>0.73</v>
       </c>
       <c r="R16">
-        <v>19.75</v>
+        <v>17.13</v>
       </c>
       <c r="S16">
         <v>20</v>
       </c>
       <c r="T16">
-        <v>-0.25</v>
+        <v>-2.87</v>
       </c>
       <c r="U16">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="V16">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W16">
-        <v>96.67</v>
+        <v>93.33</v>
       </c>
       <c r="X16">
-        <v>91.67</v>
+        <v>90</v>
       </c>
       <c r="Y16" t="str">
         <v/>
@@ -1681,10 +1681,10 @@
         <v>750</v>
       </c>
       <c r="H17">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I17">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -1696,10 +1696,10 @@
         <v>0</v>
       </c>
       <c r="M17">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="N17">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="O17">
         <v>1</v>
@@ -1708,28 +1708,28 @@
         <v>0</v>
       </c>
       <c r="Q17">
-        <v>0.7</v>
+        <v>0.65</v>
       </c>
       <c r="R17">
-        <v>19.07</v>
+        <v>20.4</v>
       </c>
       <c r="S17">
         <v>20</v>
       </c>
       <c r="T17">
-        <v>-0.93</v>
+        <v>0.4</v>
       </c>
       <c r="U17">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="V17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W17">
-        <v>90</v>
+        <v>91.67</v>
       </c>
       <c r="X17">
-        <v>86.67</v>
+        <v>95.83</v>
       </c>
       <c r="Y17" t="str">
         <v/>
@@ -1758,55 +1758,55 @@
         <v>600</v>
       </c>
       <c r="H18">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="I18">
         <v>55</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K18">
         <v>0</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="M18">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="N18">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="O18">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P18">
         <v>0</v>
       </c>
       <c r="Q18">
-        <v>0.85</v>
+        <v>3.48</v>
       </c>
       <c r="R18">
-        <v>19.5</v>
+        <v>19.17</v>
       </c>
       <c r="S18">
         <v>20</v>
       </c>
       <c r="T18">
-        <v>-0.5</v>
+        <v>-0.83</v>
       </c>
       <c r="U18">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="V18">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W18">
-        <v>85</v>
+        <v>88.33</v>
       </c>
       <c r="X18">
-        <v>92.5</v>
+        <v>88.33</v>
       </c>
       <c r="Y18" t="str">
         <v/>
@@ -1835,10 +1835,10 @@
         <v>550</v>
       </c>
       <c r="H19">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I19">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="J19">
         <v>1</v>
@@ -1847,43 +1847,43 @@
         <v>0</v>
       </c>
       <c r="L19">
-        <v>2.04</v>
+        <v>2.17</v>
       </c>
       <c r="M19">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="N19">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="O19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P19">
         <v>0</v>
       </c>
       <c r="Q19">
-        <v>3.06</v>
+        <v>2.15</v>
       </c>
       <c r="R19">
-        <v>17.82</v>
+        <v>16.91</v>
       </c>
       <c r="S19">
         <v>20</v>
       </c>
       <c r="T19">
-        <v>-2.18</v>
+        <v>-3.09</v>
       </c>
       <c r="U19">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="V19">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="W19">
-        <v>86.67</v>
+        <v>96.67</v>
       </c>
       <c r="X19">
-        <v>85.83</v>
+        <v>95</v>
       </c>
       <c r="Y19" t="str">
         <v/>
@@ -1912,55 +1912,55 @@
         <v>900</v>
       </c>
       <c r="H20">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="I20">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="J20">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K20">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L20">
-        <v>15.48</v>
+        <v>16.13</v>
       </c>
       <c r="M20">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="N20">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="O20">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="P20">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q20">
-        <v>8.14</v>
+        <v>9.94</v>
       </c>
       <c r="R20">
-        <v>19.11</v>
+        <v>20.11</v>
       </c>
       <c r="S20">
         <v>20</v>
       </c>
       <c r="T20">
-        <v>-0.89</v>
+        <v>0.11</v>
       </c>
       <c r="U20">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="V20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W20">
-        <v>85</v>
+        <v>83.33</v>
       </c>
       <c r="X20">
-        <v>86.67</v>
+        <v>88.33</v>
       </c>
       <c r="Y20" t="str">
         <v>시나리오2:불량급등</v>
@@ -1989,43 +1989,43 @@
         <v>1500</v>
       </c>
       <c r="H21">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="I21">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="J21">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K21">
         <v>0</v>
       </c>
       <c r="L21">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="M21">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="N21">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="O21">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P21">
         <v>0</v>
       </c>
       <c r="Q21">
-        <v>1</v>
+        <v>0.34</v>
       </c>
       <c r="R21">
-        <v>20.07</v>
+        <v>19.53</v>
       </c>
       <c r="S21">
         <v>20</v>
       </c>
       <c r="T21">
-        <v>0.07</v>
+        <v>-0.47</v>
       </c>
       <c r="U21">
         <v>60</v>
@@ -2037,7 +2037,7 @@
         <v>100</v>
       </c>
       <c r="X21">
-        <v>99.17</v>
+        <v>94.17</v>
       </c>
       <c r="Y21" t="str">
         <v/>
@@ -2066,55 +2066,55 @@
         <v>1400</v>
       </c>
       <c r="H22">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="I22">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="J22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K22">
         <v>0</v>
       </c>
       <c r="L22">
-        <v>0.77</v>
+        <v>1.43</v>
       </c>
       <c r="M22">
-        <v>250</v>
+        <v>269</v>
       </c>
       <c r="N22">
-        <v>249</v>
+        <v>267</v>
       </c>
       <c r="O22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P22">
         <v>0</v>
       </c>
       <c r="Q22">
-        <v>0.4</v>
+        <v>0.74</v>
       </c>
       <c r="R22">
-        <v>17.86</v>
+        <v>19.21</v>
       </c>
       <c r="S22">
         <v>20</v>
       </c>
       <c r="T22">
-        <v>-2.14</v>
+        <v>-0.79</v>
       </c>
       <c r="U22">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W22">
-        <v>100</v>
+        <v>86.67</v>
       </c>
       <c r="X22">
-        <v>91.67</v>
+        <v>88.33</v>
       </c>
       <c r="Y22" t="str">
         <v/>
@@ -2143,25 +2143,25 @@
         <v>450</v>
       </c>
       <c r="H23">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I23">
         <v>45</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23">
         <v>0</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M23">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="N23">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="O23">
         <v>1</v>
@@ -2170,28 +2170,28 @@
         <v>0</v>
       </c>
       <c r="Q23">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="R23">
-        <v>18.67</v>
+        <v>19.78</v>
       </c>
       <c r="S23">
         <v>20</v>
       </c>
       <c r="T23">
-        <v>-1.33</v>
+        <v>-0.22</v>
       </c>
       <c r="U23">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="V23">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="W23">
-        <v>95</v>
+        <v>83.33</v>
       </c>
       <c r="X23">
-        <v>90</v>
+        <v>91.67</v>
       </c>
       <c r="Y23" t="str">
         <v/>
@@ -2235,40 +2235,40 @@
         <v>2.38</v>
       </c>
       <c r="M24">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="N24">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="O24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P24">
         <v>0</v>
       </c>
       <c r="Q24">
-        <v>1.25</v>
+        <v>2.56</v>
       </c>
       <c r="R24">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="S24">
         <v>20</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="U24">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="V24">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W24">
-        <v>91.67</v>
+        <v>95</v>
       </c>
       <c r="X24">
-        <v>92.5</v>
+        <v>95</v>
       </c>
       <c r="Y24" t="str">
         <v/>
@@ -2297,55 +2297,55 @@
         <v>2000</v>
       </c>
       <c r="H25">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I25">
         <v>202</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25">
         <v>0</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>0.49</v>
       </c>
       <c r="M25">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c r="N25">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="O25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P25">
         <v>0</v>
       </c>
       <c r="Q25">
-        <v>0.27</v>
+        <v>0.52</v>
       </c>
       <c r="R25">
-        <v>18.75</v>
+        <v>19.2</v>
       </c>
       <c r="S25">
         <v>20</v>
       </c>
       <c r="T25">
-        <v>-1.25</v>
+        <v>-0.8</v>
       </c>
       <c r="U25">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="V25">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="W25">
-        <v>93.33</v>
+        <v>90</v>
       </c>
       <c r="X25">
-        <v>92.5</v>
+        <v>86.67</v>
       </c>
       <c r="Y25" t="str">
         <v/>
@@ -2374,55 +2374,55 @@
         <v>1200</v>
       </c>
       <c r="H26">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I26">
         <v>119</v>
       </c>
       <c r="J26">
+        <v>1</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+      <c r="L26">
+        <v>0.83</v>
+      </c>
+      <c r="M26">
+        <v>358</v>
+      </c>
+      <c r="N26">
+        <v>356</v>
+      </c>
+      <c r="O26">
         <v>2</v>
       </c>
-      <c r="K26">
-        <v>0</v>
-      </c>
-      <c r="L26">
-        <v>1.65</v>
-      </c>
-      <c r="M26">
-        <v>363</v>
-      </c>
-      <c r="N26">
-        <v>359</v>
-      </c>
-      <c r="O26">
-        <v>4</v>
-      </c>
       <c r="P26">
         <v>0</v>
       </c>
       <c r="Q26">
-        <v>1.1</v>
+        <v>0.56</v>
       </c>
       <c r="R26">
-        <v>30.25</v>
+        <v>29.83</v>
       </c>
       <c r="S26">
         <v>30</v>
       </c>
       <c r="T26">
-        <v>0.25</v>
+        <v>-0.17</v>
       </c>
       <c r="U26">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="V26">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W26">
-        <v>90</v>
+        <v>83.33</v>
       </c>
       <c r="X26">
-        <v>95</v>
+        <v>92.78</v>
       </c>
       <c r="Y26" t="str">
         <v/>
@@ -2451,10 +2451,10 @@
         <v>1000</v>
       </c>
       <c r="H27">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="I27">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="J27">
         <v>2</v>
@@ -2463,43 +2463,43 @@
         <v>0</v>
       </c>
       <c r="L27">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="M27">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="N27">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="O27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P27">
         <v>0</v>
       </c>
       <c r="Q27">
-        <v>1.43</v>
+        <v>1.06</v>
       </c>
       <c r="R27">
-        <v>28</v>
+        <v>28.4</v>
       </c>
       <c r="S27">
         <v>30</v>
       </c>
       <c r="T27">
-        <v>-2</v>
+        <v>-1.6</v>
       </c>
       <c r="U27">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="V27">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="W27">
-        <v>86.67</v>
+        <v>90</v>
       </c>
       <c r="X27">
-        <v>88.89</v>
+        <v>95.56</v>
       </c>
       <c r="Y27" t="str">
         <v/>
@@ -2528,10 +2528,10 @@
         <v>800</v>
       </c>
       <c r="H28">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="I28">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="J28">
         <v>1</v>
@@ -2540,13 +2540,13 @@
         <v>0</v>
       </c>
       <c r="L28">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="M28">
-        <v>232</v>
+        <v>207</v>
       </c>
       <c r="N28">
-        <v>230</v>
+        <v>205</v>
       </c>
       <c r="O28">
         <v>2</v>
@@ -2555,28 +2555,28 @@
         <v>0</v>
       </c>
       <c r="Q28">
-        <v>0.86</v>
+        <v>0.97</v>
       </c>
       <c r="R28">
-        <v>29</v>
+        <v>25.88</v>
       </c>
       <c r="S28">
         <v>30</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>-4.12</v>
       </c>
       <c r="U28">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W28">
-        <v>88.33</v>
+        <v>86.67</v>
       </c>
       <c r="X28">
-        <v>90.56</v>
+        <v>88.89</v>
       </c>
       <c r="Y28" t="str">
         <v/>
@@ -2605,10 +2605,10 @@
         <v>750</v>
       </c>
       <c r="H29">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="I29">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="J29">
         <v>1</v>
@@ -2617,13 +2617,13 @@
         <v>0</v>
       </c>
       <c r="L29">
-        <v>1.54</v>
+        <v>1.35</v>
       </c>
       <c r="M29">
-        <v>208</v>
+        <v>227</v>
       </c>
       <c r="N29">
-        <v>206</v>
+        <v>225</v>
       </c>
       <c r="O29">
         <v>2</v>
@@ -2632,28 +2632,28 @@
         <v>0</v>
       </c>
       <c r="Q29">
-        <v>0.96</v>
+        <v>0.88</v>
       </c>
       <c r="R29">
-        <v>27.73</v>
+        <v>30.27</v>
       </c>
       <c r="S29">
         <v>30</v>
       </c>
       <c r="T29">
-        <v>-2.27</v>
+        <v>0.27</v>
       </c>
       <c r="U29">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="V29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W29">
-        <v>96.67</v>
+        <v>95</v>
       </c>
       <c r="X29">
-        <v>90</v>
+        <v>95.56</v>
       </c>
       <c r="Y29" t="str">
         <v/>
@@ -2682,10 +2682,10 @@
         <v>600</v>
       </c>
       <c r="H30">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="I30">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="J30">
         <v>1</v>
@@ -2694,43 +2694,43 @@
         <v>0</v>
       </c>
       <c r="L30">
-        <v>1.89</v>
+        <v>1.64</v>
       </c>
       <c r="M30">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="N30">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="O30">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P30">
         <v>0</v>
       </c>
       <c r="Q30">
-        <v>1.18</v>
+        <v>2.84</v>
       </c>
       <c r="R30">
-        <v>28.33</v>
+        <v>29.33</v>
       </c>
       <c r="S30">
         <v>30</v>
       </c>
       <c r="T30">
-        <v>-1.67</v>
+        <v>-0.67</v>
       </c>
       <c r="U30">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="V30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W30">
-        <v>96.67</v>
+        <v>95</v>
       </c>
       <c r="X30">
-        <v>93.89</v>
+        <v>90.56</v>
       </c>
       <c r="Y30" t="str">
         <v/>
@@ -2774,40 +2774,40 @@
         <v>0</v>
       </c>
       <c r="M31">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="N31">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="O31">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P31">
         <v>0</v>
       </c>
       <c r="Q31">
-        <v>1.99</v>
+        <v>1.37</v>
       </c>
       <c r="R31">
-        <v>27.45</v>
+        <v>26.55</v>
       </c>
       <c r="S31">
         <v>30</v>
       </c>
       <c r="T31">
-        <v>-2.55</v>
+        <v>-3.45</v>
       </c>
       <c r="U31">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="V31">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="W31">
-        <v>96.67</v>
+        <v>85</v>
       </c>
       <c r="X31">
-        <v>89.44</v>
+        <v>91.67</v>
       </c>
       <c r="Y31" t="str">
         <v/>
@@ -2836,10 +2836,10 @@
         <v>900</v>
       </c>
       <c r="H32">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I32">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J32">
         <v>14</v>
@@ -2848,43 +2848,43 @@
         <v>4</v>
       </c>
       <c r="L32">
-        <v>15.73</v>
+        <v>15.91</v>
       </c>
       <c r="M32">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="N32">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="O32">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="P32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q32">
-        <v>10.73</v>
+        <v>11.9</v>
       </c>
       <c r="R32">
-        <v>29</v>
+        <v>29.89</v>
       </c>
       <c r="S32">
         <v>30</v>
       </c>
       <c r="T32">
-        <v>-1</v>
+        <v>-0.11</v>
       </c>
       <c r="U32">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="V32">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="W32">
-        <v>83.33</v>
+        <v>95</v>
       </c>
       <c r="X32">
-        <v>85.56</v>
+        <v>90.56</v>
       </c>
       <c r="Y32" t="str">
         <v>시나리오2:불량급등</v>
@@ -2913,55 +2913,55 @@
         <v>1500</v>
       </c>
       <c r="H33">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="I33">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="J33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33">
         <v>0</v>
       </c>
       <c r="L33">
-        <v>0</v>
+        <v>0.68</v>
       </c>
       <c r="M33">
-        <v>453</v>
+        <v>440</v>
       </c>
       <c r="N33">
-        <v>450</v>
+        <v>438</v>
       </c>
       <c r="O33">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P33">
         <v>0</v>
       </c>
       <c r="Q33">
-        <v>0.66</v>
+        <v>0.45</v>
       </c>
       <c r="R33">
-        <v>30.2</v>
+        <v>29.33</v>
       </c>
       <c r="S33">
         <v>30</v>
       </c>
       <c r="T33">
-        <v>0.2</v>
+        <v>-0.67</v>
       </c>
       <c r="U33">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="V33">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="W33">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="X33">
-        <v>94.44</v>
+        <v>92.78</v>
       </c>
       <c r="Y33" t="str">
         <v/>
@@ -2990,10 +2990,10 @@
         <v>1400</v>
       </c>
       <c r="H34">
-        <v>142</v>
+        <v>120</v>
       </c>
       <c r="I34">
-        <v>140</v>
+        <v>118</v>
       </c>
       <c r="J34">
         <v>2</v>
@@ -3002,43 +3002,43 @@
         <v>0</v>
       </c>
       <c r="L34">
-        <v>1.41</v>
+        <v>1.67</v>
       </c>
       <c r="M34">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="N34">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="O34">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P34">
         <v>0</v>
       </c>
       <c r="Q34">
-        <v>0.77</v>
+        <v>1.03</v>
       </c>
       <c r="R34">
-        <v>28</v>
+        <v>27.79</v>
       </c>
       <c r="S34">
         <v>30</v>
       </c>
       <c r="T34">
-        <v>-2</v>
+        <v>-2.21</v>
       </c>
       <c r="U34">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W34">
-        <v>100</v>
+        <v>93.33</v>
       </c>
       <c r="X34">
-        <v>94.44</v>
+        <v>90</v>
       </c>
       <c r="Y34" t="str">
         <v/>
@@ -3067,10 +3067,10 @@
         <v>450</v>
       </c>
       <c r="H35">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I35">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J35">
         <v>0</v>
@@ -3082,10 +3082,10 @@
         <v>0</v>
       </c>
       <c r="M35">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="N35">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="O35">
         <v>1</v>
@@ -3094,28 +3094,28 @@
         <v>0</v>
       </c>
       <c r="Q35">
-        <v>0.81</v>
+        <v>0.77</v>
       </c>
       <c r="R35">
-        <v>27.56</v>
+        <v>28.89</v>
       </c>
       <c r="S35">
         <v>30</v>
       </c>
       <c r="T35">
-        <v>-2.44</v>
+        <v>-1.11</v>
       </c>
       <c r="U35">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="V35">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W35">
-        <v>90</v>
+        <v>83.33</v>
       </c>
       <c r="X35">
-        <v>90</v>
+        <v>88.89</v>
       </c>
       <c r="Y35" t="str">
         <v/>
@@ -3144,55 +3144,55 @@
         <v>400</v>
       </c>
       <c r="H36">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I36">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J36">
         <v>0</v>
       </c>
       <c r="K36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L36">
         <v>0</v>
       </c>
       <c r="M36">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="N36">
         <v>96</v>
       </c>
       <c r="O36">
+        <v>2</v>
+      </c>
+      <c r="P36">
         <v>1</v>
       </c>
-      <c r="P36">
-        <v>0</v>
-      </c>
       <c r="Q36">
-        <v>1.03</v>
+        <v>2.02</v>
       </c>
       <c r="R36">
-        <v>24.25</v>
+        <v>24.75</v>
       </c>
       <c r="S36">
         <v>30</v>
       </c>
       <c r="T36">
-        <v>-5.75</v>
+        <v>-5.25</v>
       </c>
       <c r="U36">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="V36">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="W36">
-        <v>83.33</v>
+        <v>76.67</v>
       </c>
       <c r="X36">
-        <v>89.44</v>
+        <v>88.89</v>
       </c>
       <c r="Y36" t="str">
         <v>시나리오4:작업자교체(복합)</v>
@@ -3221,10 +3221,10 @@
         <v>2000</v>
       </c>
       <c r="H37">
-        <v>204</v>
+        <v>183</v>
       </c>
       <c r="I37">
-        <v>204</v>
+        <v>183</v>
       </c>
       <c r="J37">
         <v>0</v>
@@ -3236,28 +3236,28 @@
         <v>0</v>
       </c>
       <c r="M37">
-        <v>579</v>
+        <v>567</v>
       </c>
       <c r="N37">
-        <v>578</v>
+        <v>565</v>
       </c>
       <c r="O37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P37">
         <v>0</v>
       </c>
       <c r="Q37">
-        <v>0.17</v>
+        <v>0.35</v>
       </c>
       <c r="R37">
-        <v>28.95</v>
+        <v>28.35</v>
       </c>
       <c r="S37">
         <v>30</v>
       </c>
       <c r="T37">
-        <v>-1.05</v>
+        <v>-1.65</v>
       </c>
       <c r="U37">
         <v>52</v>
@@ -3269,7 +3269,7 @@
         <v>86.67</v>
       </c>
       <c r="X37">
-        <v>90.56</v>
+        <v>86.67</v>
       </c>
       <c r="Y37" t="str">
         <v/>
@@ -3298,52 +3298,52 @@
         <v>1200</v>
       </c>
       <c r="H38">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="I38">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="J38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38">
         <v>0</v>
       </c>
       <c r="L38">
-        <v>0</v>
+        <v>0.93</v>
       </c>
       <c r="M38">
-        <v>489</v>
+        <v>465</v>
       </c>
       <c r="N38">
-        <v>485</v>
+        <v>462</v>
       </c>
       <c r="O38">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P38">
         <v>0</v>
       </c>
       <c r="Q38">
-        <v>0.82</v>
+        <v>0.65</v>
       </c>
       <c r="R38">
-        <v>40.75</v>
+        <v>38.75</v>
       </c>
       <c r="S38">
         <v>40</v>
       </c>
       <c r="T38">
-        <v>0.75</v>
+        <v>-1.25</v>
       </c>
       <c r="U38">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="V38">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="W38">
-        <v>90</v>
+        <v>96.67</v>
       </c>
       <c r="X38">
         <v>93.75</v>
@@ -3375,25 +3375,25 @@
         <v>1000</v>
       </c>
       <c r="H39">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="I39">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="J39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K39">
         <v>0</v>
       </c>
       <c r="L39">
-        <v>0</v>
+        <v>0.97</v>
       </c>
       <c r="M39">
-        <v>368</v>
+        <v>387</v>
       </c>
       <c r="N39">
-        <v>364</v>
+        <v>383</v>
       </c>
       <c r="O39">
         <v>4</v>
@@ -3402,28 +3402,28 @@
         <v>0</v>
       </c>
       <c r="Q39">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="R39">
-        <v>36.8</v>
+        <v>38.7</v>
       </c>
       <c r="S39">
         <v>40</v>
       </c>
       <c r="T39">
-        <v>-3.2</v>
+        <v>-1.3</v>
       </c>
       <c r="U39">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="V39">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W39">
-        <v>88.33</v>
+        <v>85</v>
       </c>
       <c r="X39">
-        <v>88.75</v>
+        <v>92.92</v>
       </c>
       <c r="Y39" t="str">
         <v/>
@@ -3452,55 +3452,55 @@
         <v>800</v>
       </c>
       <c r="H40">
+        <v>4</v>
+      </c>
+      <c r="I40">
         <v>3</v>
       </c>
-      <c r="I40">
+      <c r="J40">
         <v>1</v>
       </c>
-      <c r="J40">
-        <v>2</v>
-      </c>
       <c r="K40">
         <v>0</v>
       </c>
       <c r="L40">
-        <v>66.67</v>
+        <v>25</v>
       </c>
       <c r="M40">
-        <v>235</v>
+        <v>211</v>
       </c>
       <c r="N40">
-        <v>231</v>
+        <v>208</v>
       </c>
       <c r="O40">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P40">
         <v>0</v>
       </c>
       <c r="Q40">
-        <v>1.7</v>
+        <v>1.42</v>
       </c>
       <c r="R40">
-        <v>29.38</v>
+        <v>26.38</v>
       </c>
       <c r="S40">
         <v>40</v>
       </c>
       <c r="T40">
-        <v>-10.62</v>
+        <v>-13.62</v>
       </c>
       <c r="U40">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="V40">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="W40">
-        <v>26.67</v>
+        <v>21.67</v>
       </c>
       <c r="X40">
-        <v>74.58</v>
+        <v>72.08</v>
       </c>
       <c r="Y40" t="str">
         <v>시나리오1:설비고장(급감)</v>
@@ -3529,10 +3529,10 @@
         <v>750</v>
       </c>
       <c r="H41">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="I41">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="J41">
         <v>1</v>
@@ -3541,13 +3541,13 @@
         <v>0</v>
       </c>
       <c r="L41">
-        <v>1.59</v>
+        <v>1.35</v>
       </c>
       <c r="M41">
-        <v>271</v>
+        <v>301</v>
       </c>
       <c r="N41">
-        <v>268</v>
+        <v>298</v>
       </c>
       <c r="O41">
         <v>3</v>
@@ -3556,28 +3556,28 @@
         <v>0</v>
       </c>
       <c r="Q41">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="R41">
-        <v>36.13</v>
+        <v>40.13</v>
       </c>
       <c r="S41">
         <v>40</v>
       </c>
       <c r="T41">
-        <v>-3.87</v>
+        <v>0.13</v>
       </c>
       <c r="U41">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="V41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W41">
-        <v>98.33</v>
+        <v>100</v>
       </c>
       <c r="X41">
-        <v>92.08</v>
+        <v>96.67</v>
       </c>
       <c r="Y41" t="str">
         <v/>
@@ -3606,10 +3606,10 @@
         <v>600</v>
       </c>
       <c r="H42">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="I42">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="J42">
         <v>0</v>
@@ -3621,40 +3621,40 @@
         <v>0</v>
       </c>
       <c r="M42">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="N42">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="O42">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P42">
         <v>0</v>
       </c>
       <c r="Q42">
-        <v>0.87</v>
+        <v>2.09</v>
       </c>
       <c r="R42">
-        <v>38.33</v>
+        <v>39.83</v>
       </c>
       <c r="S42">
         <v>40</v>
       </c>
       <c r="T42">
-        <v>-1.67</v>
+        <v>-0.17</v>
       </c>
       <c r="U42">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="V42">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W42">
-        <v>90</v>
+        <v>83.33</v>
       </c>
       <c r="X42">
-        <v>92.92</v>
+        <v>88.75</v>
       </c>
       <c r="Y42" t="str">
         <v/>
@@ -3683,10 +3683,10 @@
         <v>550</v>
       </c>
       <c r="H43">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="I43">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="J43">
         <v>2</v>
@@ -3695,43 +3695,43 @@
         <v>0</v>
       </c>
       <c r="L43">
-        <v>4.08</v>
+        <v>3.51</v>
       </c>
       <c r="M43">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="N43">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="O43">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P43">
         <v>0</v>
       </c>
       <c r="Q43">
-        <v>2.5</v>
+        <v>1.97</v>
       </c>
       <c r="R43">
-        <v>36.36</v>
+        <v>36.91</v>
       </c>
       <c r="S43">
         <v>40</v>
       </c>
       <c r="T43">
-        <v>-3.64</v>
+        <v>-3.09</v>
       </c>
       <c r="U43">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="V43">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W43">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="X43">
-        <v>88.33</v>
+        <v>93.75</v>
       </c>
       <c r="Y43" t="str">
         <v/>
@@ -3760,10 +3760,10 @@
         <v>900</v>
       </c>
       <c r="H44">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I44">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="J44">
         <v>13</v>
@@ -3772,43 +3772,43 @@
         <v>4</v>
       </c>
       <c r="L44">
-        <v>15.48</v>
+        <v>15.85</v>
       </c>
       <c r="M44">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="N44">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="O44">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="P44">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q44">
-        <v>11.88</v>
+        <v>12.82</v>
       </c>
       <c r="R44">
-        <v>38.33</v>
+        <v>39</v>
       </c>
       <c r="S44">
         <v>40</v>
       </c>
       <c r="T44">
-        <v>-1.67</v>
+        <v>-1</v>
       </c>
       <c r="U44">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="V44">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="W44">
-        <v>88.33</v>
+        <v>96.67</v>
       </c>
       <c r="X44">
-        <v>86.25</v>
+        <v>92.08</v>
       </c>
       <c r="Y44" t="str">
         <v>시나리오2:불량급등</v>
@@ -3837,10 +3837,10 @@
         <v>1500</v>
       </c>
       <c r="H45">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="I45">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="J45">
         <v>0</v>
@@ -3852,40 +3852,40 @@
         <v>0</v>
       </c>
       <c r="M45">
-        <v>602</v>
+        <v>597</v>
       </c>
       <c r="N45">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="O45">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P45">
         <v>0</v>
       </c>
       <c r="Q45">
-        <v>0.5</v>
+        <v>0.34</v>
       </c>
       <c r="R45">
-        <v>40.13</v>
+        <v>39.8</v>
       </c>
       <c r="S45">
         <v>40</v>
       </c>
       <c r="T45">
-        <v>0.13</v>
+        <v>-0.2</v>
       </c>
       <c r="U45">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="V45">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W45">
-        <v>96.67</v>
+        <v>93.33</v>
       </c>
       <c r="X45">
-        <v>95</v>
+        <v>92.92</v>
       </c>
       <c r="Y45" t="str">
         <v/>
@@ -3914,43 +3914,43 @@
         <v>1400</v>
       </c>
       <c r="H46">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="I46">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="J46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K46">
         <v>0</v>
       </c>
       <c r="L46">
-        <v>0</v>
+        <v>0.82</v>
       </c>
       <c r="M46">
-        <v>528</v>
+        <v>511</v>
       </c>
       <c r="N46">
-        <v>525</v>
+        <v>506</v>
       </c>
       <c r="O46">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P46">
         <v>0</v>
       </c>
       <c r="Q46">
-        <v>0.57</v>
+        <v>0.98</v>
       </c>
       <c r="R46">
-        <v>37.71</v>
+        <v>36.5</v>
       </c>
       <c r="S46">
         <v>40</v>
       </c>
       <c r="T46">
-        <v>-2.29</v>
+        <v>-3.5</v>
       </c>
       <c r="U46">
         <v>55</v>
@@ -3962,7 +3962,7 @@
         <v>91.67</v>
       </c>
       <c r="X46">
-        <v>93.75</v>
+        <v>90.42</v>
       </c>
       <c r="Y46" t="str">
         <v/>
@@ -3991,52 +3991,52 @@
         <v>450</v>
       </c>
       <c r="H47">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="I47">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K47">
         <v>0</v>
       </c>
       <c r="L47">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M47">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="N47">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="O47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P47">
         <v>0</v>
       </c>
       <c r="Q47">
-        <v>0.6</v>
+        <v>1.14</v>
       </c>
       <c r="R47">
-        <v>37.11</v>
+        <v>38.89</v>
       </c>
       <c r="S47">
         <v>40</v>
       </c>
       <c r="T47">
-        <v>-2.89</v>
+        <v>-1.11</v>
       </c>
       <c r="U47">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="V47">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W47">
-        <v>85</v>
+        <v>88.33</v>
       </c>
       <c r="X47">
         <v>88.75</v>
@@ -4068,55 +4068,55 @@
         <v>400</v>
       </c>
       <c r="H48">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="I48">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="J48">
         <v>0</v>
       </c>
       <c r="K48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L48">
         <v>0</v>
       </c>
       <c r="M48">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="N48">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="O48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P48">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q48">
-        <v>0.84</v>
+        <v>1.74</v>
       </c>
       <c r="R48">
-        <v>29.75</v>
+        <v>28.75</v>
       </c>
       <c r="S48">
         <v>40</v>
       </c>
       <c r="T48">
-        <v>-10.25</v>
+        <v>-11.25</v>
       </c>
       <c r="U48">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="V48">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="W48">
-        <v>91.67</v>
+        <v>70</v>
       </c>
       <c r="X48">
-        <v>90</v>
+        <v>84.17</v>
       </c>
       <c r="Y48" t="str">
         <v>시나리오4:작업자교체(복합)</v>
@@ -4145,10 +4145,10 @@
         <v>2000</v>
       </c>
       <c r="H49">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="I49">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="J49">
         <v>0</v>
@@ -4160,40 +4160,40 @@
         <v>0</v>
       </c>
       <c r="M49">
-        <v>754</v>
+        <v>772</v>
       </c>
       <c r="N49">
-        <v>753</v>
+        <v>770</v>
       </c>
       <c r="O49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P49">
         <v>0</v>
       </c>
       <c r="Q49">
-        <v>0.13</v>
+        <v>0.26</v>
       </c>
       <c r="R49">
-        <v>37.7</v>
+        <v>38.6</v>
       </c>
       <c r="S49">
         <v>40</v>
       </c>
       <c r="T49">
-        <v>-2.3</v>
+        <v>-1.4</v>
       </c>
       <c r="U49">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="V49">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="W49">
-        <v>86.67</v>
+        <v>93.33</v>
       </c>
       <c r="X49">
-        <v>89.58</v>
+        <v>88.33</v>
       </c>
       <c r="Y49" t="str">
         <v/>
@@ -4222,25 +4222,25 @@
         <v>1200</v>
       </c>
       <c r="H50">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="I50">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="J50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K50">
         <v>0</v>
       </c>
       <c r="L50">
-        <v>0.98</v>
+        <v>1.71</v>
       </c>
       <c r="M50">
-        <v>591</v>
+        <v>582</v>
       </c>
       <c r="N50">
-        <v>586</v>
+        <v>577</v>
       </c>
       <c r="O50">
         <v>5</v>
@@ -4249,28 +4249,28 @@
         <v>0</v>
       </c>
       <c r="Q50">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="R50">
-        <v>49.25</v>
+        <v>48.5</v>
       </c>
       <c r="S50">
         <v>50</v>
       </c>
       <c r="T50">
-        <v>-0.75</v>
+        <v>-1.5</v>
       </c>
       <c r="U50">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="V50">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="W50">
-        <v>98.33</v>
+        <v>91.67</v>
       </c>
       <c r="X50">
-        <v>94.67</v>
+        <v>93.33</v>
       </c>
       <c r="Y50" t="str">
         <v/>
@@ -4299,55 +4299,55 @@
         <v>1000</v>
       </c>
       <c r="H51">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="I51">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="J51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K51">
         <v>0</v>
       </c>
       <c r="L51">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="M51">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="N51">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="O51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P51">
         <v>0</v>
       </c>
       <c r="Q51">
-        <v>0.85</v>
+        <v>1.05</v>
       </c>
       <c r="R51">
-        <v>47.2</v>
+        <v>47.6</v>
       </c>
       <c r="S51">
         <v>50</v>
       </c>
       <c r="T51">
-        <v>-2.8</v>
+        <v>-2.4</v>
       </c>
       <c r="U51">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="V51">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="W51">
-        <v>98.33</v>
+        <v>90</v>
       </c>
       <c r="X51">
-        <v>90.67</v>
+        <v>92.33</v>
       </c>
       <c r="Y51" t="str">
         <v/>
@@ -4391,28 +4391,28 @@
         <v>0</v>
       </c>
       <c r="M52">
-        <v>235</v>
+        <v>211</v>
       </c>
       <c r="N52">
-        <v>231</v>
+        <v>208</v>
       </c>
       <c r="O52">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P52">
         <v>0</v>
       </c>
       <c r="Q52">
-        <v>1.7</v>
+        <v>1.42</v>
       </c>
       <c r="R52">
-        <v>29.38</v>
+        <v>26.38</v>
       </c>
       <c r="S52">
         <v>50</v>
       </c>
       <c r="T52">
-        <v>-20.62</v>
+        <v>-23.62</v>
       </c>
       <c r="U52">
         <v>0</v>
@@ -4424,7 +4424,7 @@
         <v>0</v>
       </c>
       <c r="X52">
-        <v>59.67</v>
+        <v>57.67</v>
       </c>
       <c r="Y52" t="str">
         <v>시나리오1:설비고장(정지)</v>
@@ -4453,10 +4453,10 @@
         <v>750</v>
       </c>
       <c r="H53">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="I53">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="J53">
         <v>1</v>
@@ -4465,13 +4465,13 @@
         <v>0</v>
       </c>
       <c r="L53">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="M53">
-        <v>341</v>
+        <v>378</v>
       </c>
       <c r="N53">
-        <v>337</v>
+        <v>374</v>
       </c>
       <c r="O53">
         <v>4</v>
@@ -4480,28 +4480,28 @@
         <v>0</v>
       </c>
       <c r="Q53">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="R53">
-        <v>45.47</v>
+        <v>50.4</v>
       </c>
       <c r="S53">
         <v>50</v>
       </c>
       <c r="T53">
-        <v>-4.53</v>
+        <v>0.4</v>
       </c>
       <c r="U53">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="V53">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="W53">
-        <v>98.33</v>
+        <v>88.33</v>
       </c>
       <c r="X53">
-        <v>93.33</v>
+        <v>95</v>
       </c>
       <c r="Y53" t="str">
         <v/>
@@ -4530,55 +4530,55 @@
         <v>600</v>
       </c>
       <c r="H54">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="I54">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="J54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K54">
         <v>0</v>
       </c>
       <c r="L54">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="M54">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="N54">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="O54">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="P54">
         <v>0</v>
       </c>
       <c r="Q54">
-        <v>0.69</v>
+        <v>2.07</v>
       </c>
       <c r="R54">
-        <v>48</v>
+        <v>48.33</v>
       </c>
       <c r="S54">
         <v>50</v>
       </c>
       <c r="T54">
-        <v>-2</v>
+        <v>-1.67</v>
       </c>
       <c r="U54">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="V54">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W54">
-        <v>85</v>
+        <v>88.33</v>
       </c>
       <c r="X54">
-        <v>91.33</v>
+        <v>88.67</v>
       </c>
       <c r="Y54" t="str">
         <v/>
@@ -4607,10 +4607,10 @@
         <v>550</v>
       </c>
       <c r="H55">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="I55">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="J55">
         <v>2</v>
@@ -4619,43 +4619,43 @@
         <v>0</v>
       </c>
       <c r="L55">
-        <v>4.35</v>
+        <v>3.7</v>
       </c>
       <c r="M55">
-        <v>246</v>
+        <v>257</v>
       </c>
       <c r="N55">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="O55">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P55">
         <v>0</v>
       </c>
       <c r="Q55">
-        <v>2.85</v>
+        <v>2.33</v>
       </c>
       <c r="R55">
-        <v>44.73</v>
+        <v>46.73</v>
       </c>
       <c r="S55">
         <v>50</v>
       </c>
       <c r="T55">
-        <v>-5.27</v>
+        <v>-3.27</v>
       </c>
       <c r="U55">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="V55">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="W55">
-        <v>86.67</v>
+        <v>90</v>
       </c>
       <c r="X55">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="Y55" t="str">
         <v/>
@@ -4684,10 +4684,10 @@
         <v>900</v>
       </c>
       <c r="H56">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I56">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J56">
         <v>7</v>
@@ -4696,43 +4696,43 @@
         <v>1</v>
       </c>
       <c r="L56">
-        <v>8.54</v>
+        <v>8.43</v>
       </c>
       <c r="M56">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="N56">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="O56">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="P56">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q56">
-        <v>11.24</v>
+        <v>11.98</v>
       </c>
       <c r="R56">
-        <v>47.44</v>
+        <v>48.22</v>
       </c>
       <c r="S56">
         <v>50</v>
       </c>
       <c r="T56">
-        <v>-2.56</v>
+        <v>-1.78</v>
       </c>
       <c r="U56">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="V56">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W56">
-        <v>85</v>
+        <v>83.33</v>
       </c>
       <c r="X56">
-        <v>86</v>
+        <v>90.33</v>
       </c>
       <c r="Y56" t="str">
         <v>시나리오2:불량급등(개선중)</v>
@@ -4761,10 +4761,10 @@
         <v>1500</v>
       </c>
       <c r="H57">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="I57">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="J57">
         <v>2</v>
@@ -4773,43 +4773,43 @@
         <v>0</v>
       </c>
       <c r="L57">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="M57">
-        <v>758</v>
+        <v>741</v>
       </c>
       <c r="N57">
-        <v>753</v>
+        <v>737</v>
       </c>
       <c r="O57">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P57">
         <v>0</v>
       </c>
       <c r="Q57">
-        <v>0.66</v>
+        <v>0.54</v>
       </c>
       <c r="R57">
-        <v>50.53</v>
+        <v>49.4</v>
       </c>
       <c r="S57">
         <v>50</v>
       </c>
       <c r="T57">
-        <v>0.53</v>
+        <v>-0.6</v>
       </c>
       <c r="U57">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="V57">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W57">
-        <v>93.33</v>
+        <v>100</v>
       </c>
       <c r="X57">
-        <v>94.67</v>
+        <v>94.33</v>
       </c>
       <c r="Y57" t="str">
         <v/>
@@ -4838,55 +4838,55 @@
         <v>1400</v>
       </c>
       <c r="H58">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="I58">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="J58">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K58">
         <v>0</v>
       </c>
       <c r="L58">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M58">
-        <v>650</v>
+        <v>642</v>
       </c>
       <c r="N58">
-        <v>647</v>
+        <v>635</v>
       </c>
       <c r="O58">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="P58">
         <v>0</v>
       </c>
       <c r="Q58">
-        <v>0.46</v>
+        <v>1.09</v>
       </c>
       <c r="R58">
-        <v>46.43</v>
+        <v>45.86</v>
       </c>
       <c r="S58">
         <v>50</v>
       </c>
       <c r="T58">
-        <v>-3.57</v>
+        <v>-4.14</v>
       </c>
       <c r="U58">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="V58">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="W58">
-        <v>96.67</v>
+        <v>83.33</v>
       </c>
       <c r="X58">
-        <v>94.33</v>
+        <v>89</v>
       </c>
       <c r="Y58" t="str">
         <v/>
@@ -4915,10 +4915,10 @@
         <v>450</v>
       </c>
       <c r="H59">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="I59">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J59">
         <v>0</v>
@@ -4930,40 +4930,40 @@
         <v>0</v>
       </c>
       <c r="M59">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="N59">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="O59">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P59">
         <v>0</v>
       </c>
       <c r="Q59">
-        <v>0.48</v>
+        <v>0.91</v>
       </c>
       <c r="R59">
-        <v>46.22</v>
+        <v>48.67</v>
       </c>
       <c r="S59">
         <v>50</v>
       </c>
       <c r="T59">
-        <v>-3.78</v>
+        <v>-1.33</v>
       </c>
       <c r="U59">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="V59">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W59">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="X59">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Y59" t="str">
         <v/>
@@ -4992,10 +4992,10 @@
         <v>400</v>
       </c>
       <c r="H60">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I60">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J60">
         <v>0</v>
@@ -5010,16 +5010,16 @@
         <v>135</v>
       </c>
       <c r="N60">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="O60">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P60">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q60">
-        <v>0.74</v>
+        <v>1.48</v>
       </c>
       <c r="R60">
         <v>33.75</v>
@@ -5031,16 +5031,16 @@
         <v>-16.25</v>
       </c>
       <c r="U60">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="V60">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="W60">
-        <v>68.33</v>
+        <v>88.33</v>
       </c>
       <c r="X60">
-        <v>85.67</v>
+        <v>85</v>
       </c>
       <c r="Y60" t="str">
         <v>시나리오4:작업자교체(복합)</v>
@@ -5069,10 +5069,10 @@
         <v>2000</v>
       </c>
       <c r="H61">
-        <v>176</v>
+        <v>197</v>
       </c>
       <c r="I61">
-        <v>175</v>
+        <v>196</v>
       </c>
       <c r="J61">
         <v>1</v>
@@ -5081,43 +5081,43 @@
         <v>0</v>
       </c>
       <c r="L61">
-        <v>0.57</v>
+        <v>0.51</v>
       </c>
       <c r="M61">
-        <v>930</v>
+        <v>969</v>
       </c>
       <c r="N61">
-        <v>928</v>
+        <v>966</v>
       </c>
       <c r="O61">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P61">
         <v>0</v>
       </c>
       <c r="Q61">
-        <v>0.22</v>
+        <v>0.31</v>
       </c>
       <c r="R61">
-        <v>46.5</v>
+        <v>48.45</v>
       </c>
       <c r="S61">
         <v>50</v>
       </c>
       <c r="T61">
-        <v>-3.5</v>
+        <v>-1.55</v>
       </c>
       <c r="U61">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="V61">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="W61">
-        <v>83.33</v>
+        <v>98.33</v>
       </c>
       <c r="X61">
-        <v>88.33</v>
+        <v>90.33</v>
       </c>
       <c r="Y61" t="str">
         <v/>
@@ -5146,34 +5146,34 @@
         <v>1200</v>
       </c>
       <c r="H62">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="I62">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="J62">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K62">
         <v>0</v>
       </c>
       <c r="L62">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M62">
         <v>696</v>
       </c>
       <c r="N62">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="O62">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P62">
         <v>0</v>
       </c>
       <c r="Q62">
-        <v>1.01</v>
+        <v>0.72</v>
       </c>
       <c r="R62">
         <v>58</v>
@@ -5185,13 +5185,13 @@
         <v>-2</v>
       </c>
       <c r="U62">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="V62">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W62">
-        <v>93.33</v>
+        <v>100</v>
       </c>
       <c r="X62">
         <v>94.44</v>
@@ -5223,55 +5223,55 @@
         <v>1000</v>
       </c>
       <c r="H63">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I63">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="J63">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K63">
         <v>0</v>
       </c>
       <c r="L63">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M63">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="N63">
         <v>565</v>
       </c>
       <c r="O63">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="P63">
         <v>0</v>
       </c>
       <c r="Q63">
-        <v>0.7</v>
+        <v>1.22</v>
       </c>
       <c r="R63">
-        <v>56.9</v>
+        <v>57.2</v>
       </c>
       <c r="S63">
         <v>60</v>
       </c>
       <c r="T63">
-        <v>-3.1</v>
+        <v>-2.8</v>
       </c>
       <c r="U63">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="V63">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W63">
-        <v>93.33</v>
+        <v>95</v>
       </c>
       <c r="X63">
-        <v>91.11</v>
+        <v>92.78</v>
       </c>
       <c r="Y63" t="str">
         <v/>
@@ -5315,28 +5315,28 @@
         <v>0</v>
       </c>
       <c r="M64">
-        <v>235</v>
+        <v>211</v>
       </c>
       <c r="N64">
-        <v>231</v>
+        <v>208</v>
       </c>
       <c r="O64">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P64">
         <v>0</v>
       </c>
       <c r="Q64">
-        <v>1.7</v>
+        <v>1.42</v>
       </c>
       <c r="R64">
-        <v>29.38</v>
+        <v>26.38</v>
       </c>
       <c r="S64">
         <v>60</v>
       </c>
       <c r="T64">
-        <v>-30.62</v>
+        <v>-33.62</v>
       </c>
       <c r="U64">
         <v>0</v>
@@ -5348,7 +5348,7 @@
         <v>0</v>
       </c>
       <c r="X64">
-        <v>49.72</v>
+        <v>48.06</v>
       </c>
       <c r="Y64" t="str">
         <v>시나리오1:설비고장(정지)</v>
@@ -5377,10 +5377,10 @@
         <v>750</v>
       </c>
       <c r="H65">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I65">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J65">
         <v>1</v>
@@ -5389,13 +5389,13 @@
         <v>0</v>
       </c>
       <c r="L65">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="M65">
-        <v>407</v>
+        <v>443</v>
       </c>
       <c r="N65">
-        <v>402</v>
+        <v>438</v>
       </c>
       <c r="O65">
         <v>5</v>
@@ -5404,28 +5404,28 @@
         <v>0</v>
       </c>
       <c r="Q65">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="R65">
-        <v>54.27</v>
+        <v>59.07</v>
       </c>
       <c r="S65">
         <v>60</v>
       </c>
       <c r="T65">
-        <v>-5.73</v>
+        <v>-0.93</v>
       </c>
       <c r="U65">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="V65">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W65">
-        <v>98.33</v>
+        <v>93.33</v>
       </c>
       <c r="X65">
-        <v>94.17</v>
+        <v>94.72</v>
       </c>
       <c r="Y65" t="str">
         <v/>
@@ -5454,10 +5454,10 @@
         <v>600</v>
       </c>
       <c r="H66">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="I66">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="J66">
         <v>1</v>
@@ -5466,43 +5466,43 @@
         <v>0</v>
       </c>
       <c r="L66">
-        <v>1.89</v>
+        <v>1.64</v>
       </c>
       <c r="M66">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="N66">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="O66">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="P66">
         <v>0</v>
       </c>
       <c r="Q66">
-        <v>0.88</v>
+        <v>1.99</v>
       </c>
       <c r="R66">
-        <v>56.83</v>
+        <v>58.5</v>
       </c>
       <c r="S66">
         <v>60</v>
       </c>
       <c r="T66">
-        <v>-3.17</v>
+        <v>-1.5</v>
       </c>
       <c r="U66">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="V66">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="W66">
-        <v>93.33</v>
+        <v>85</v>
       </c>
       <c r="X66">
-        <v>91.67</v>
+        <v>88.06</v>
       </c>
       <c r="Y66" t="str">
         <v/>
@@ -5531,55 +5531,55 @@
         <v>550</v>
       </c>
       <c r="H67">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I67">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J67">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K67">
         <v>0</v>
       </c>
       <c r="L67">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="M67">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="N67">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c r="O67">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P67">
         <v>0</v>
       </c>
       <c r="Q67">
-        <v>2.71</v>
+        <v>1.97</v>
       </c>
       <c r="R67">
-        <v>53.64</v>
+        <v>55.27</v>
       </c>
       <c r="S67">
         <v>60</v>
       </c>
       <c r="T67">
-        <v>-6.36</v>
+        <v>-4.73</v>
       </c>
       <c r="U67">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="V67">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W67">
-        <v>88.33</v>
+        <v>83.33</v>
       </c>
       <c r="X67">
-        <v>88.06</v>
+        <v>91.39</v>
       </c>
       <c r="Y67" t="str">
         <v/>
@@ -5611,52 +5611,52 @@
         <v>89</v>
       </c>
       <c r="I68">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J68">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K68">
         <v>0</v>
       </c>
       <c r="L68">
-        <v>2.25</v>
+        <v>1.12</v>
       </c>
       <c r="M68">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="N68">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="O68">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="P68">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q68">
-        <v>9.69</v>
+        <v>10.13</v>
       </c>
       <c r="R68">
-        <v>57.33</v>
+        <v>58.11</v>
       </c>
       <c r="S68">
         <v>60</v>
       </c>
       <c r="T68">
-        <v>-2.67</v>
+        <v>-1.89</v>
       </c>
       <c r="U68">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="V68">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="W68">
-        <v>91.67</v>
+        <v>85</v>
       </c>
       <c r="X68">
-        <v>86.94</v>
+        <v>89.44</v>
       </c>
       <c r="Y68" t="str">
         <v/>
@@ -5685,55 +5685,55 @@
         <v>1500</v>
       </c>
       <c r="H69">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="I69">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="J69">
+        <v>5</v>
+      </c>
+      <c r="K69">
+        <v>2</v>
+      </c>
+      <c r="L69">
+        <v>11.9</v>
+      </c>
+      <c r="M69">
+        <v>783</v>
+      </c>
+      <c r="N69">
+        <v>772</v>
+      </c>
+      <c r="O69">
         <v>9</v>
       </c>
-      <c r="K69">
-        <v>5</v>
-      </c>
-      <c r="L69">
-        <v>16.67</v>
-      </c>
-      <c r="M69">
-        <v>812</v>
-      </c>
-      <c r="N69">
-        <v>793</v>
-      </c>
-      <c r="O69">
-        <v>14</v>
-      </c>
       <c r="P69">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q69">
-        <v>1.72</v>
+        <v>1.15</v>
       </c>
       <c r="R69">
-        <v>54.13</v>
+        <v>52.2</v>
       </c>
       <c r="S69">
         <v>60</v>
       </c>
       <c r="T69">
-        <v>-5.87</v>
+        <v>-7.8</v>
       </c>
       <c r="U69">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="V69">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="W69">
-        <v>50</v>
+        <v>63.33</v>
       </c>
       <c r="X69">
-        <v>87.22</v>
+        <v>89.17</v>
       </c>
       <c r="Y69" t="str">
         <v>시나리오3:금형이상(급감)</v>
@@ -5762,55 +5762,55 @@
         <v>1400</v>
       </c>
       <c r="H70">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="I70">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="J70">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K70">
         <v>0</v>
       </c>
       <c r="L70">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="M70">
-        <v>790</v>
+        <v>772</v>
       </c>
       <c r="N70">
-        <v>787</v>
+        <v>763</v>
       </c>
       <c r="O70">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="P70">
         <v>0</v>
       </c>
       <c r="Q70">
-        <v>0.38</v>
+        <v>1.17</v>
       </c>
       <c r="R70">
-        <v>56.43</v>
+        <v>55.14</v>
       </c>
       <c r="S70">
         <v>60</v>
       </c>
       <c r="T70">
-        <v>-3.57</v>
+        <v>-4.86</v>
       </c>
       <c r="U70">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="V70">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="W70">
-        <v>96.67</v>
+        <v>86.67</v>
       </c>
       <c r="X70">
-        <v>94.72</v>
+        <v>88.61</v>
       </c>
       <c r="Y70" t="str">
         <v/>
@@ -5839,10 +5839,10 @@
         <v>450</v>
       </c>
       <c r="H71">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="I71">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="J71">
         <v>1</v>
@@ -5851,31 +5851,31 @@
         <v>0</v>
       </c>
       <c r="L71">
-        <v>2.17</v>
+        <v>2.56</v>
       </c>
       <c r="M71">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="N71">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="O71">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P71">
         <v>0</v>
       </c>
       <c r="Q71">
-        <v>0.79</v>
+        <v>1.16</v>
       </c>
       <c r="R71">
-        <v>56.44</v>
+        <v>57.33</v>
       </c>
       <c r="S71">
         <v>60</v>
       </c>
       <c r="T71">
-        <v>-3.56</v>
+        <v>-2.67</v>
       </c>
       <c r="U71">
         <v>59</v>
@@ -5887,7 +5887,7 @@
         <v>98.33</v>
       </c>
       <c r="X71">
-        <v>91.39</v>
+        <v>92.22</v>
       </c>
       <c r="Y71" t="str">
         <v/>
@@ -5934,16 +5934,16 @@
         <v>175</v>
       </c>
       <c r="N72">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="O72">
+        <v>3</v>
+      </c>
+      <c r="P72">
         <v>2</v>
       </c>
-      <c r="P72">
-        <v>0</v>
-      </c>
       <c r="Q72">
-        <v>1.14</v>
+        <v>1.71</v>
       </c>
       <c r="R72">
         <v>43.75</v>
@@ -5964,7 +5964,7 @@
         <v>88.33</v>
       </c>
       <c r="X72">
-        <v>86.11</v>
+        <v>85.56</v>
       </c>
       <c r="Y72" t="str">
         <v/>
@@ -5993,55 +5993,55 @@
         <v>2000</v>
       </c>
       <c r="H73">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I73">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="J73">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K73">
         <v>0</v>
       </c>
       <c r="L73">
-        <v>0</v>
+        <v>0.58</v>
       </c>
       <c r="M73">
-        <v>1103</v>
+        <v>1140</v>
       </c>
       <c r="N73">
-        <v>1101</v>
+        <v>1136</v>
       </c>
       <c r="O73">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P73">
         <v>0</v>
       </c>
       <c r="Q73">
-        <v>0.18</v>
+        <v>0.35</v>
       </c>
       <c r="R73">
-        <v>55.15</v>
+        <v>57</v>
       </c>
       <c r="S73">
         <v>60</v>
       </c>
       <c r="T73">
-        <v>-4.85</v>
+        <v>-3</v>
       </c>
       <c r="U73">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="V73">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W73">
-        <v>83.33</v>
+        <v>86.67</v>
       </c>
       <c r="X73">
-        <v>87.5</v>
+        <v>89.72</v>
       </c>
       <c r="Y73" t="str">
         <v/>
@@ -6070,55 +6070,55 @@
         <v>1200</v>
       </c>
       <c r="H74">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I74">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="J74">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K74">
         <v>0</v>
       </c>
       <c r="L74">
-        <v>0.83</v>
+        <v>1.68</v>
       </c>
       <c r="M74">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="N74">
         <v>808</v>
       </c>
       <c r="O74">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P74">
         <v>0</v>
       </c>
       <c r="Q74">
-        <v>0.98</v>
+        <v>0.86</v>
       </c>
       <c r="R74">
-        <v>68</v>
+        <v>67.92</v>
       </c>
       <c r="S74">
         <v>70</v>
       </c>
       <c r="T74">
-        <v>-2</v>
+        <v>-2.08</v>
       </c>
       <c r="U74">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="V74">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="W74">
-        <v>85</v>
+        <v>96.67</v>
       </c>
       <c r="X74">
-        <v>93.1</v>
+        <v>94.76</v>
       </c>
       <c r="Y74" t="str">
         <v/>
@@ -6147,10 +6147,10 @@
         <v>1000</v>
       </c>
       <c r="H75">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="I75">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="J75">
         <v>0</v>
@@ -6162,40 +6162,40 @@
         <v>0</v>
       </c>
       <c r="M75">
-        <v>668</v>
+        <v>661</v>
       </c>
       <c r="N75">
-        <v>664</v>
+        <v>654</v>
       </c>
       <c r="O75">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="P75">
         <v>0</v>
       </c>
       <c r="Q75">
-        <v>0.6</v>
+        <v>1.06</v>
       </c>
       <c r="R75">
-        <v>66.8</v>
+        <v>66.1</v>
       </c>
       <c r="S75">
         <v>70</v>
       </c>
       <c r="T75">
-        <v>-3.2</v>
+        <v>-3.9</v>
       </c>
       <c r="U75">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="V75">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="W75">
-        <v>98.33</v>
+        <v>91.67</v>
       </c>
       <c r="X75">
-        <v>92.14</v>
+        <v>92.62</v>
       </c>
       <c r="Y75" t="str">
         <v/>
@@ -6224,25 +6224,25 @@
         <v>800</v>
       </c>
       <c r="H76">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I76">
         <v>15</v>
       </c>
       <c r="J76">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K76">
         <v>0</v>
       </c>
       <c r="L76">
-        <v>11.76</v>
+        <v>16.67</v>
       </c>
       <c r="M76">
-        <v>252</v>
+        <v>229</v>
       </c>
       <c r="N76">
-        <v>246</v>
+        <v>223</v>
       </c>
       <c r="O76">
         <v>6</v>
@@ -6251,25 +6251,25 @@
         <v>0</v>
       </c>
       <c r="Q76">
-        <v>2.38</v>
+        <v>2.62</v>
       </c>
       <c r="R76">
-        <v>31.5</v>
+        <v>28.63</v>
       </c>
       <c r="S76">
         <v>70</v>
       </c>
       <c r="T76">
-        <v>-38.5</v>
+        <v>-41.37</v>
       </c>
       <c r="U76">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="V76">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="W76">
-        <v>36.67</v>
+        <v>46.67</v>
       </c>
       <c r="X76">
         <v>47.86</v>
@@ -6301,55 +6301,55 @@
         <v>750</v>
       </c>
       <c r="H77">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="I77">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="J77">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K77">
         <v>0</v>
       </c>
       <c r="L77">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="M77">
-        <v>470</v>
+        <v>513</v>
       </c>
       <c r="N77">
-        <v>464</v>
+        <v>508</v>
       </c>
       <c r="O77">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P77">
         <v>0</v>
       </c>
       <c r="Q77">
-        <v>1.28</v>
+        <v>0.97</v>
       </c>
       <c r="R77">
-        <v>62.67</v>
+        <v>68.4</v>
       </c>
       <c r="S77">
         <v>70</v>
       </c>
       <c r="T77">
-        <v>-7.33</v>
+        <v>-1.6</v>
       </c>
       <c r="U77">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="V77">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="W77">
-        <v>95</v>
+        <v>83.33</v>
       </c>
       <c r="X77">
-        <v>94.29</v>
+        <v>93.1</v>
       </c>
       <c r="Y77" t="str">
         <v/>
@@ -6378,55 +6378,55 @@
         <v>600</v>
       </c>
       <c r="H78">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="I78">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="J78">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K78">
         <v>0</v>
       </c>
       <c r="L78">
-        <v>1.82</v>
+        <v>3.28</v>
       </c>
       <c r="M78">
-        <v>396</v>
+        <v>412</v>
       </c>
       <c r="N78">
-        <v>392</v>
+        <v>403</v>
       </c>
       <c r="O78">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="P78">
         <v>0</v>
       </c>
       <c r="Q78">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="R78">
-        <v>66</v>
+        <v>68.67</v>
       </c>
       <c r="S78">
         <v>70</v>
       </c>
       <c r="T78">
-        <v>-4</v>
+        <v>-1.33</v>
       </c>
       <c r="U78">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="V78">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="W78">
-        <v>93.33</v>
+        <v>86.67</v>
       </c>
       <c r="X78">
-        <v>91.9</v>
+        <v>87.86</v>
       </c>
       <c r="Y78" t="str">
         <v/>
@@ -6455,10 +6455,10 @@
         <v>550</v>
       </c>
       <c r="H79">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="I79">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="J79">
         <v>2</v>
@@ -6467,43 +6467,43 @@
         <v>0</v>
       </c>
       <c r="L79">
-        <v>3.77</v>
+        <v>4</v>
       </c>
       <c r="M79">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="N79">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="O79">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="P79">
         <v>0</v>
       </c>
       <c r="Q79">
-        <v>2.87</v>
+        <v>2.26</v>
       </c>
       <c r="R79">
-        <v>63.27</v>
+        <v>64.36</v>
       </c>
       <c r="S79">
         <v>70</v>
       </c>
       <c r="T79">
-        <v>-6.73</v>
+        <v>-5.64</v>
       </c>
       <c r="U79">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="V79">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W79">
-        <v>83.33</v>
+        <v>85</v>
       </c>
       <c r="X79">
-        <v>87.38</v>
+        <v>90.48</v>
       </c>
       <c r="Y79" t="str">
         <v/>
@@ -6532,55 +6532,55 @@
         <v>900</v>
       </c>
       <c r="H80">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="I80">
         <v>81</v>
       </c>
       <c r="J80">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K80">
         <v>0</v>
       </c>
       <c r="L80">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M80">
-        <v>597</v>
+        <v>606</v>
       </c>
       <c r="N80">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="O80">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="P80">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q80">
-        <v>8.38</v>
+        <v>9.08</v>
       </c>
       <c r="R80">
-        <v>66.33</v>
+        <v>67.33</v>
       </c>
       <c r="S80">
         <v>70</v>
       </c>
       <c r="T80">
-        <v>-3.67</v>
+        <v>-2.67</v>
       </c>
       <c r="U80">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="V80">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W80">
-        <v>96.67</v>
+        <v>95</v>
       </c>
       <c r="X80">
-        <v>88.33</v>
+        <v>90.24</v>
       </c>
       <c r="Y80" t="str">
         <v/>
@@ -6609,55 +6609,55 @@
         <v>1500</v>
       </c>
       <c r="H81">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="I81">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="J81">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K81">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L81">
-        <v>29.41</v>
+        <v>40.74</v>
       </c>
       <c r="M81">
-        <v>846</v>
+        <v>810</v>
       </c>
       <c r="N81">
-        <v>812</v>
+        <v>782</v>
       </c>
       <c r="O81">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="P81">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Q81">
-        <v>2.84</v>
+        <v>2.47</v>
       </c>
       <c r="R81">
-        <v>56.4</v>
+        <v>54</v>
       </c>
       <c r="S81">
         <v>70</v>
       </c>
       <c r="T81">
-        <v>-13.6</v>
+        <v>-16</v>
       </c>
       <c r="U81">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="V81">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="W81">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="X81">
-        <v>81.9</v>
+        <v>82.86</v>
       </c>
       <c r="Y81" t="str">
         <v>시나리오3:금형이상(심화)</v>
@@ -6686,55 +6686,55 @@
         <v>1400</v>
       </c>
       <c r="H82">
-        <v>146</v>
+        <v>120</v>
       </c>
       <c r="I82">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="J82">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K82">
         <v>0</v>
       </c>
       <c r="L82">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="M82">
-        <v>936</v>
+        <v>892</v>
       </c>
       <c r="N82">
-        <v>931</v>
+        <v>883</v>
       </c>
       <c r="O82">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="P82">
         <v>0</v>
       </c>
       <c r="Q82">
-        <v>0.53</v>
+        <v>1.01</v>
       </c>
       <c r="R82">
-        <v>66.86</v>
+        <v>63.71</v>
       </c>
       <c r="S82">
         <v>70</v>
       </c>
       <c r="T82">
-        <v>-3.14</v>
+        <v>-6.29</v>
       </c>
       <c r="U82">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="V82">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="W82">
-        <v>86.67</v>
+        <v>95</v>
       </c>
       <c r="X82">
-        <v>93.57</v>
+        <v>89.52</v>
       </c>
       <c r="Y82" t="str">
         <v/>
@@ -6763,25 +6763,25 @@
         <v>450</v>
       </c>
       <c r="H83">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="I83">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J83">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K83">
         <v>0</v>
       </c>
       <c r="L83">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="M83">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="N83">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="O83">
         <v>3</v>
@@ -6790,28 +6790,28 @@
         <v>0</v>
       </c>
       <c r="Q83">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="R83">
-        <v>65.11</v>
+        <v>66.67</v>
       </c>
       <c r="S83">
         <v>70</v>
       </c>
       <c r="T83">
-        <v>-4.89</v>
+        <v>-3.33</v>
       </c>
       <c r="U83">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="V83">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W83">
-        <v>95</v>
+        <v>93.33</v>
       </c>
       <c r="X83">
-        <v>91.9</v>
+        <v>92.38</v>
       </c>
       <c r="Y83" t="str">
         <v/>
@@ -6840,55 +6840,55 @@
         <v>400</v>
       </c>
       <c r="H84">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I84">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="J84">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K84">
         <v>0</v>
       </c>
       <c r="L84">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="M84">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N84">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="O84">
         <v>3</v>
       </c>
       <c r="P84">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q84">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="R84">
-        <v>53.25</v>
+        <v>53.5</v>
       </c>
       <c r="S84">
         <v>70</v>
       </c>
       <c r="T84">
-        <v>-16.75</v>
+        <v>-16.5</v>
       </c>
       <c r="U84">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="V84">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W84">
-        <v>95</v>
+        <v>96.67</v>
       </c>
       <c r="X84">
-        <v>87.38</v>
+        <v>87.14</v>
       </c>
       <c r="Y84" t="str">
         <v/>
@@ -6920,52 +6920,52 @@
         <v>204</v>
       </c>
       <c r="I85">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="J85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K85">
         <v>0</v>
       </c>
       <c r="L85">
-        <v>0</v>
+        <v>0.49</v>
       </c>
       <c r="M85">
-        <v>1307</v>
+        <v>1344</v>
       </c>
       <c r="N85">
-        <v>1305</v>
+        <v>1339</v>
       </c>
       <c r="O85">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P85">
         <v>0</v>
       </c>
       <c r="Q85">
-        <v>0.15</v>
+        <v>0.37</v>
       </c>
       <c r="R85">
-        <v>65.35</v>
+        <v>67.2</v>
       </c>
       <c r="S85">
         <v>70</v>
       </c>
       <c r="T85">
-        <v>-4.65</v>
+        <v>-2.8</v>
       </c>
       <c r="U85">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="V85">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W85">
-        <v>100</v>
+        <v>88.33</v>
       </c>
       <c r="X85">
-        <v>89.29</v>
+        <v>89.52</v>
       </c>
       <c r="Y85" t="str">
         <v/>
@@ -6994,10 +6994,10 @@
         <v>1200</v>
       </c>
       <c r="H86">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I86">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J86">
         <v>2</v>
@@ -7006,43 +7006,43 @@
         <v>0</v>
       </c>
       <c r="L86">
-        <v>10.53</v>
+        <v>11.76</v>
       </c>
       <c r="M86">
-        <v>835</v>
+        <v>832</v>
       </c>
       <c r="N86">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="O86">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P86">
         <v>0</v>
       </c>
       <c r="Q86">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="R86">
-        <v>69.58</v>
+        <v>69.33</v>
       </c>
       <c r="S86">
         <v>80</v>
       </c>
       <c r="T86">
-        <v>-10.42</v>
+        <v>-10.67</v>
       </c>
       <c r="U86">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="V86">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="W86">
-        <v>21.67</v>
+        <v>25</v>
       </c>
       <c r="X86">
-        <v>84.17</v>
+        <v>86.04</v>
       </c>
       <c r="Y86" t="str">
         <v>시나리오5:자재대기(급락)</v>
@@ -7071,10 +7071,10 @@
         <v>1000</v>
       </c>
       <c r="H87">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="I87">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="J87">
         <v>2</v>
@@ -7083,22 +7083,22 @@
         <v>0</v>
       </c>
       <c r="L87">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="M87">
         <v>757</v>
       </c>
       <c r="N87">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="O87">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P87">
         <v>0</v>
       </c>
       <c r="Q87">
-        <v>0.79</v>
+        <v>1.19</v>
       </c>
       <c r="R87">
         <v>75.7</v>
@@ -7110,16 +7110,16 @@
         <v>-4.3</v>
       </c>
       <c r="U87">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="V87">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="W87">
-        <v>85</v>
+        <v>91.67</v>
       </c>
       <c r="X87">
-        <v>91.25</v>
+        <v>92.5</v>
       </c>
       <c r="Y87" t="str">
         <v/>
@@ -7148,55 +7148,55 @@
         <v>800</v>
       </c>
       <c r="H88">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I88">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="J88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K88">
         <v>0</v>
       </c>
       <c r="L88">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M88">
-        <v>322</v>
+        <v>298</v>
       </c>
       <c r="N88">
-        <v>316</v>
+        <v>291</v>
       </c>
       <c r="O88">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P88">
         <v>0</v>
       </c>
       <c r="Q88">
-        <v>1.86</v>
+        <v>2.35</v>
       </c>
       <c r="R88">
-        <v>40.25</v>
+        <v>37.25</v>
       </c>
       <c r="S88">
         <v>80</v>
       </c>
       <c r="T88">
-        <v>-39.75</v>
+        <v>-42.75</v>
       </c>
       <c r="U88">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="V88">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="W88">
-        <v>96.67</v>
+        <v>90</v>
       </c>
       <c r="X88">
-        <v>53.96</v>
+        <v>53.13</v>
       </c>
       <c r="Y88" t="str">
         <v/>
@@ -7225,10 +7225,10 @@
         <v>750</v>
       </c>
       <c r="H89">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="I89">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="J89">
         <v>1</v>
@@ -7237,43 +7237,43 @@
         <v>0</v>
       </c>
       <c r="L89">
-        <v>1.3</v>
+        <v>1.59</v>
       </c>
       <c r="M89">
-        <v>547</v>
+        <v>576</v>
       </c>
       <c r="N89">
-        <v>540</v>
+        <v>570</v>
       </c>
       <c r="O89">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P89">
         <v>0</v>
       </c>
       <c r="Q89">
-        <v>1.28</v>
+        <v>1.04</v>
       </c>
       <c r="R89">
-        <v>72.93</v>
+        <v>76.8</v>
       </c>
       <c r="S89">
         <v>80</v>
       </c>
       <c r="T89">
-        <v>-7.07</v>
+        <v>-3.2</v>
       </c>
       <c r="U89">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="V89">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W89">
-        <v>100</v>
+        <v>96.67</v>
       </c>
       <c r="X89">
-        <v>95</v>
+        <v>93.54</v>
       </c>
       <c r="Y89" t="str">
         <v/>
@@ -7302,55 +7302,55 @@
         <v>600</v>
       </c>
       <c r="H90">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I90">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="J90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K90">
         <v>0</v>
       </c>
       <c r="L90">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="M90">
-        <v>459</v>
+        <v>473</v>
       </c>
       <c r="N90">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="O90">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="P90">
         <v>0</v>
       </c>
       <c r="Q90">
-        <v>0.87</v>
+        <v>2.11</v>
       </c>
       <c r="R90">
-        <v>76.5</v>
+        <v>78.83</v>
       </c>
       <c r="S90">
         <v>80</v>
       </c>
       <c r="T90">
-        <v>-3.5</v>
+        <v>-1.17</v>
       </c>
       <c r="U90">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="V90">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W90">
-        <v>100</v>
+        <v>96.67</v>
       </c>
       <c r="X90">
-        <v>92.92</v>
+        <v>88.96</v>
       </c>
       <c r="Y90" t="str">
         <v/>
@@ -7379,10 +7379,10 @@
         <v>550</v>
       </c>
       <c r="H91">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="I91">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="J91">
         <v>1</v>
@@ -7391,43 +7391,43 @@
         <v>0</v>
       </c>
       <c r="L91">
-        <v>2.04</v>
+        <v>1.82</v>
       </c>
       <c r="M91">
-        <v>397</v>
+        <v>409</v>
       </c>
       <c r="N91">
-        <v>386</v>
+        <v>400</v>
       </c>
       <c r="O91">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="P91">
         <v>0</v>
       </c>
       <c r="Q91">
-        <v>2.77</v>
+        <v>2.2</v>
       </c>
       <c r="R91">
-        <v>72.18</v>
+        <v>74.36</v>
       </c>
       <c r="S91">
         <v>80</v>
       </c>
       <c r="T91">
-        <v>-7.82</v>
+        <v>-5.64</v>
       </c>
       <c r="U91">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="V91">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="W91">
-        <v>91.67</v>
+        <v>85</v>
       </c>
       <c r="X91">
-        <v>87.92</v>
+        <v>89.79</v>
       </c>
       <c r="Y91" t="str">
         <v/>
@@ -7456,55 +7456,55 @@
         <v>900</v>
       </c>
       <c r="H92">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="I92">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="J92">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K92">
         <v>0</v>
       </c>
       <c r="L92">
-        <v>2.22</v>
+        <v>3.49</v>
       </c>
       <c r="M92">
-        <v>687</v>
+        <v>692</v>
       </c>
       <c r="N92">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="O92">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="P92">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q92">
-        <v>7.57</v>
+        <v>8.38</v>
       </c>
       <c r="R92">
-        <v>76.33</v>
+        <v>76.89</v>
       </c>
       <c r="S92">
         <v>80</v>
       </c>
       <c r="T92">
-        <v>-3.67</v>
+        <v>-3.11</v>
       </c>
       <c r="U92">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="V92">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="W92">
-        <v>96.67</v>
+        <v>90</v>
       </c>
       <c r="X92">
-        <v>89.38</v>
+        <v>90.21</v>
       </c>
       <c r="Y92" t="str">
         <v/>
@@ -7533,52 +7533,52 @@
         <v>1500</v>
       </c>
       <c r="H93">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="I93">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="J93">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K93">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L93">
-        <v>3.16</v>
+        <v>4.35</v>
       </c>
       <c r="M93">
-        <v>941</v>
+        <v>902</v>
       </c>
       <c r="N93">
-        <v>903</v>
+        <v>868</v>
       </c>
       <c r="O93">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="P93">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q93">
-        <v>2.87</v>
+        <v>2.66</v>
       </c>
       <c r="R93">
-        <v>62.73</v>
+        <v>60.13</v>
       </c>
       <c r="S93">
         <v>80</v>
       </c>
       <c r="T93">
-        <v>-17.27</v>
+        <v>-19.87</v>
       </c>
       <c r="U93">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="V93">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="W93">
-        <v>76.67</v>
+        <v>70</v>
       </c>
       <c r="X93">
         <v>81.25</v>
@@ -7610,55 +7610,55 @@
         <v>1400</v>
       </c>
       <c r="H94">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="I94">
         <v>140</v>
       </c>
       <c r="J94">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K94">
         <v>0</v>
       </c>
       <c r="L94">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="M94">
-        <v>1078</v>
+        <v>1032</v>
       </c>
       <c r="N94">
-        <v>1071</v>
+        <v>1023</v>
       </c>
       <c r="O94">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P94">
         <v>0</v>
       </c>
       <c r="Q94">
-        <v>0.65</v>
+        <v>0.87</v>
       </c>
       <c r="R94">
-        <v>77</v>
+        <v>73.71</v>
       </c>
       <c r="S94">
         <v>80</v>
       </c>
       <c r="T94">
-        <v>-3</v>
+        <v>-6.29</v>
       </c>
       <c r="U94">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="V94">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W94">
-        <v>91.67</v>
+        <v>100</v>
       </c>
       <c r="X94">
-        <v>93.33</v>
+        <v>90.83</v>
       </c>
       <c r="Y94" t="str">
         <v/>
@@ -7687,10 +7687,10 @@
         <v>450</v>
       </c>
       <c r="H95">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="I95">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="J95">
         <v>0</v>
@@ -7702,10 +7702,10 @@
         <v>0</v>
       </c>
       <c r="M95">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="N95">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="O95">
         <v>3</v>
@@ -7717,25 +7717,25 @@
         <v>0.88</v>
       </c>
       <c r="R95">
-        <v>75.56</v>
+        <v>75.78</v>
       </c>
       <c r="S95">
         <v>80</v>
       </c>
       <c r="T95">
-        <v>-4.44</v>
+        <v>-4.22</v>
       </c>
       <c r="U95">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="V95">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="W95">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="X95">
-        <v>91.04</v>
+        <v>92.71</v>
       </c>
       <c r="Y95" t="str">
         <v/>
@@ -7764,10 +7764,10 @@
         <v>400</v>
       </c>
       <c r="H96">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="I96">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="J96">
         <v>1</v>
@@ -7776,31 +7776,31 @@
         <v>0</v>
       </c>
       <c r="L96">
-        <v>2.94</v>
+        <v>2.44</v>
       </c>
       <c r="M96">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="N96">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="O96">
         <v>4</v>
       </c>
       <c r="P96">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q96">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="R96">
-        <v>61.75</v>
+        <v>63.75</v>
       </c>
       <c r="S96">
         <v>80</v>
       </c>
       <c r="T96">
-        <v>-18.25</v>
+        <v>-16.25</v>
       </c>
       <c r="U96">
         <v>56</v>
@@ -7812,7 +7812,7 @@
         <v>93.33</v>
       </c>
       <c r="X96">
-        <v>88.13</v>
+        <v>87.92</v>
       </c>
       <c r="Y96" t="str">
         <v/>
@@ -7841,55 +7841,55 @@
         <v>2000</v>
       </c>
       <c r="H97">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="I97">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="J97">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K97">
         <v>0</v>
       </c>
       <c r="L97">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="M97">
-        <v>1495</v>
+        <v>1542</v>
       </c>
       <c r="N97">
-        <v>1493</v>
+        <v>1536</v>
       </c>
       <c r="O97">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="P97">
         <v>0</v>
       </c>
       <c r="Q97">
-        <v>0.13</v>
+        <v>0.39</v>
       </c>
       <c r="R97">
-        <v>74.75</v>
+        <v>77.1</v>
       </c>
       <c r="S97">
         <v>80</v>
       </c>
       <c r="T97">
-        <v>-5.25</v>
+        <v>-2.9</v>
       </c>
       <c r="U97">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="V97">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W97">
-        <v>96.67</v>
+        <v>91.67</v>
       </c>
       <c r="X97">
-        <v>90.21</v>
+        <v>89.79</v>
       </c>
       <c r="Y97" t="str">
         <v/>
@@ -7921,22 +7921,22 @@
         <v>8</v>
       </c>
       <c r="I98">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J98">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K98">
         <v>0</v>
       </c>
       <c r="L98">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="M98">
-        <v>843</v>
+        <v>840</v>
       </c>
       <c r="N98">
-        <v>833</v>
+        <v>830</v>
       </c>
       <c r="O98">
         <v>10</v>
@@ -7948,25 +7948,25 @@
         <v>1.19</v>
       </c>
       <c r="R98">
-        <v>70.25</v>
+        <v>70</v>
       </c>
       <c r="S98">
         <v>90</v>
       </c>
       <c r="T98">
-        <v>-19.75</v>
+        <v>-20</v>
       </c>
       <c r="U98">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V98">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="W98">
-        <v>13.33</v>
+        <v>11.67</v>
       </c>
       <c r="X98">
-        <v>76.3</v>
+        <v>77.78</v>
       </c>
       <c r="Y98" t="str">
         <v>시나리오5:자재대기(대기중)</v>
@@ -7995,10 +7995,10 @@
         <v>1000</v>
       </c>
       <c r="H99">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="I99">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="J99">
         <v>0</v>
@@ -8010,40 +8010,40 @@
         <v>0</v>
       </c>
       <c r="M99">
-        <v>850</v>
+        <v>843</v>
       </c>
       <c r="N99">
-        <v>844</v>
+        <v>834</v>
       </c>
       <c r="O99">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P99">
         <v>0</v>
       </c>
       <c r="Q99">
-        <v>0.71</v>
+        <v>1.07</v>
       </c>
       <c r="R99">
-        <v>85</v>
+        <v>84.3</v>
       </c>
       <c r="S99">
         <v>90</v>
       </c>
       <c r="T99">
-        <v>-5</v>
+        <v>-5.7</v>
       </c>
       <c r="U99">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="V99">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W99">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="X99">
-        <v>90.56</v>
+        <v>93.33</v>
       </c>
       <c r="Y99" t="str">
         <v/>
@@ -8072,25 +8072,25 @@
         <v>800</v>
       </c>
       <c r="H100">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="I100">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="J100">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K100">
         <v>0</v>
       </c>
       <c r="L100">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="M100">
-        <v>396</v>
+        <v>376</v>
       </c>
       <c r="N100">
-        <v>389</v>
+        <v>369</v>
       </c>
       <c r="O100">
         <v>7</v>
@@ -8099,28 +8099,28 @@
         <v>0</v>
       </c>
       <c r="Q100">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="R100">
-        <v>49.5</v>
+        <v>47</v>
       </c>
       <c r="S100">
         <v>90</v>
       </c>
       <c r="T100">
-        <v>-40.5</v>
+        <v>-43</v>
       </c>
       <c r="U100">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="V100">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W100">
-        <v>90</v>
+        <v>88.33</v>
       </c>
       <c r="X100">
-        <v>57.96</v>
+        <v>57.04</v>
       </c>
       <c r="Y100" t="str">
         <v/>
@@ -8149,55 +8149,55 @@
         <v>750</v>
       </c>
       <c r="H101">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="I101">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="J101">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K101">
         <v>0</v>
       </c>
       <c r="L101">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="M101">
-        <v>621</v>
+        <v>642</v>
       </c>
       <c r="N101">
-        <v>613</v>
+        <v>636</v>
       </c>
       <c r="O101">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P101">
         <v>0</v>
       </c>
       <c r="Q101">
-        <v>1.29</v>
+        <v>0.93</v>
       </c>
       <c r="R101">
-        <v>82.8</v>
+        <v>85.6</v>
       </c>
       <c r="S101">
         <v>90</v>
       </c>
       <c r="T101">
-        <v>-7.2</v>
+        <v>-4.4</v>
       </c>
       <c r="U101">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="V101">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W101">
-        <v>88.33</v>
+        <v>85</v>
       </c>
       <c r="X101">
-        <v>94.26</v>
+        <v>92.59</v>
       </c>
       <c r="Y101" t="str">
         <v/>
@@ -8226,55 +8226,55 @@
         <v>600</v>
       </c>
       <c r="H102">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="I102">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="J102">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K102">
         <v>0</v>
       </c>
       <c r="L102">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="M102">
-        <v>518</v>
+        <v>535</v>
       </c>
       <c r="N102">
-        <v>512</v>
+        <v>525</v>
       </c>
       <c r="O102">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="P102">
         <v>0</v>
       </c>
       <c r="Q102">
-        <v>1.16</v>
+        <v>1.87</v>
       </c>
       <c r="R102">
-        <v>86.33</v>
+        <v>89.17</v>
       </c>
       <c r="S102">
         <v>90</v>
       </c>
       <c r="T102">
-        <v>-3.67</v>
+        <v>-0.83</v>
       </c>
       <c r="U102">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="V102">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="W102">
-        <v>86.67</v>
+        <v>90</v>
       </c>
       <c r="X102">
-        <v>92.22</v>
+        <v>89.07</v>
       </c>
       <c r="Y102" t="str">
         <v/>
@@ -8303,55 +8303,55 @@
         <v>550</v>
       </c>
       <c r="H103">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="I103">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="J103">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K103">
         <v>0</v>
       </c>
       <c r="L103">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M103">
-        <v>443</v>
+        <v>464</v>
       </c>
       <c r="N103">
-        <v>432</v>
+        <v>454</v>
       </c>
       <c r="O103">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P103">
         <v>0</v>
       </c>
       <c r="Q103">
-        <v>2.48</v>
+        <v>2.16</v>
       </c>
       <c r="R103">
-        <v>80.55</v>
+        <v>84.36</v>
       </c>
       <c r="S103">
         <v>90</v>
       </c>
       <c r="T103">
-        <v>-9.45</v>
+        <v>-5.64</v>
       </c>
       <c r="U103">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="V103">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="W103">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="X103">
-        <v>87.59</v>
+        <v>90.37</v>
       </c>
       <c r="Y103" t="str">
         <v/>
@@ -8380,10 +8380,10 @@
         <v>900</v>
       </c>
       <c r="H104">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="I104">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="J104">
         <v>1</v>
@@ -8392,43 +8392,43 @@
         <v>0</v>
       </c>
       <c r="L104">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="M104">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="N104">
-        <v>711</v>
+        <v>705</v>
       </c>
       <c r="O104">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="P104">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q104">
-        <v>6.82</v>
+        <v>7.58</v>
       </c>
       <c r="R104">
-        <v>86.33</v>
+        <v>86.44</v>
       </c>
       <c r="S104">
         <v>90</v>
       </c>
       <c r="T104">
-        <v>-3.67</v>
+        <v>-3.56</v>
       </c>
       <c r="U104">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="V104">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="W104">
-        <v>88.33</v>
+        <v>93.33</v>
       </c>
       <c r="X104">
-        <v>89.26</v>
+        <v>90.56</v>
       </c>
       <c r="Y104" t="str">
         <v/>
@@ -8457,10 +8457,10 @@
         <v>1500</v>
       </c>
       <c r="H105">
-        <v>156</v>
+        <v>132</v>
       </c>
       <c r="I105">
-        <v>154</v>
+        <v>130</v>
       </c>
       <c r="J105">
         <v>2</v>
@@ -8469,31 +8469,31 @@
         <v>0</v>
       </c>
       <c r="L105">
-        <v>1.28</v>
+        <v>1.52</v>
       </c>
       <c r="M105">
-        <v>1097</v>
+        <v>1034</v>
       </c>
       <c r="N105">
-        <v>1057</v>
+        <v>998</v>
       </c>
       <c r="O105">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="P105">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q105">
-        <v>2.64</v>
+        <v>2.51</v>
       </c>
       <c r="R105">
-        <v>73.13</v>
+        <v>68.93</v>
       </c>
       <c r="S105">
         <v>90</v>
       </c>
       <c r="T105">
-        <v>-16.87</v>
+        <v>-21.07</v>
       </c>
       <c r="U105">
         <v>60</v>
@@ -8534,55 +8534,55 @@
         <v>1400</v>
       </c>
       <c r="H106">
-        <v>144</v>
+        <v>122</v>
       </c>
       <c r="I106">
-        <v>143</v>
+        <v>120</v>
       </c>
       <c r="J106">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K106">
         <v>0</v>
       </c>
       <c r="L106">
-        <v>0.69</v>
+        <v>1.64</v>
       </c>
       <c r="M106">
-        <v>1222</v>
+        <v>1154</v>
       </c>
       <c r="N106">
-        <v>1214</v>
+        <v>1143</v>
       </c>
       <c r="O106">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="P106">
         <v>0</v>
       </c>
       <c r="Q106">
-        <v>0.65</v>
+        <v>0.95</v>
       </c>
       <c r="R106">
-        <v>87.29</v>
+        <v>82.43</v>
       </c>
       <c r="S106">
         <v>90</v>
       </c>
       <c r="T106">
-        <v>-2.71</v>
+        <v>-7.57</v>
       </c>
       <c r="U106">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="V106">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="W106">
-        <v>86.67</v>
+        <v>95</v>
       </c>
       <c r="X106">
-        <v>92.59</v>
+        <v>91.3</v>
       </c>
       <c r="Y106" t="str">
         <v/>
@@ -8611,55 +8611,55 @@
         <v>450</v>
       </c>
       <c r="H107">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="I107">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="J107">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K107">
         <v>0</v>
       </c>
       <c r="L107">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M107">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="N107">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="O107">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P107">
         <v>0</v>
       </c>
       <c r="Q107">
-        <v>1.03</v>
+        <v>0.79</v>
       </c>
       <c r="R107">
-        <v>86</v>
+        <v>84.44</v>
       </c>
       <c r="S107">
         <v>90</v>
       </c>
       <c r="T107">
-        <v>-4</v>
+        <v>-5.56</v>
       </c>
       <c r="U107">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="V107">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W107">
-        <v>83.33</v>
+        <v>90</v>
       </c>
       <c r="X107">
-        <v>90.19</v>
+        <v>92.41</v>
       </c>
       <c r="Y107" t="str">
         <v/>
@@ -8703,40 +8703,40 @@
         <v>0</v>
       </c>
       <c r="M108">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="N108">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="O108">
         <v>4</v>
       </c>
       <c r="P108">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q108">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="R108">
-        <v>71.5</v>
+        <v>73.5</v>
       </c>
       <c r="S108">
         <v>90</v>
       </c>
       <c r="T108">
-        <v>-18.5</v>
+        <v>-16.5</v>
       </c>
       <c r="U108">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="V108">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="W108">
-        <v>86.67</v>
+        <v>93.33</v>
       </c>
       <c r="X108">
-        <v>87.96</v>
+        <v>88.52</v>
       </c>
       <c r="Y108" t="str">
         <v/>
@@ -8765,55 +8765,55 @@
         <v>2000</v>
       </c>
       <c r="H109">
-        <v>202</v>
+        <v>177</v>
       </c>
       <c r="I109">
-        <v>202</v>
+        <v>176</v>
       </c>
       <c r="J109">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K109">
         <v>0</v>
       </c>
       <c r="L109">
-        <v>0</v>
+        <v>0.56</v>
       </c>
       <c r="M109">
-        <v>1697</v>
+        <v>1719</v>
       </c>
       <c r="N109">
-        <v>1695</v>
+        <v>1712</v>
       </c>
       <c r="O109">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="P109">
         <v>0</v>
       </c>
       <c r="Q109">
-        <v>0.12</v>
+        <v>0.41</v>
       </c>
       <c r="R109">
-        <v>84.85</v>
+        <v>85.95</v>
       </c>
       <c r="S109">
         <v>90</v>
       </c>
       <c r="T109">
-        <v>-5.15</v>
+        <v>-4.05</v>
       </c>
       <c r="U109">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="V109">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W109">
-        <v>85</v>
+        <v>86.67</v>
       </c>
       <c r="X109">
-        <v>89.63</v>
+        <v>89.44</v>
       </c>
       <c r="Y109" t="str">
         <v/>
@@ -8842,55 +8842,55 @@
         <v>1200</v>
       </c>
       <c r="H110">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="I110">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="J110">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K110">
         <v>0</v>
       </c>
       <c r="L110">
-        <v>5.66</v>
+        <v>1.47</v>
       </c>
       <c r="M110">
-        <v>896</v>
+        <v>908</v>
       </c>
       <c r="N110">
-        <v>883</v>
+        <v>897</v>
       </c>
       <c r="O110">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="P110">
         <v>0</v>
       </c>
       <c r="Q110">
-        <v>1.45</v>
+        <v>1.21</v>
       </c>
       <c r="R110">
-        <v>74.67</v>
+        <v>75.67</v>
       </c>
       <c r="S110">
         <v>100</v>
       </c>
       <c r="T110">
-        <v>-25.33</v>
+        <v>-24.33</v>
       </c>
       <c r="U110">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="V110">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="W110">
-        <v>48.33</v>
+        <v>46.67</v>
       </c>
       <c r="X110">
-        <v>73.5</v>
+        <v>74.67</v>
       </c>
       <c r="Y110" t="str">
         <v>시나리오5:자재대기(일부입고)</v>
@@ -8919,55 +8919,55 @@
         <v>1000</v>
       </c>
       <c r="H111">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="I111">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="J111">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K111">
         <v>0</v>
       </c>
       <c r="L111">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="M111">
-        <v>947</v>
+        <v>937</v>
       </c>
       <c r="N111">
-        <v>940</v>
+        <v>928</v>
       </c>
       <c r="O111">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P111">
         <v>0</v>
       </c>
       <c r="Q111">
-        <v>0.74</v>
+        <v>0.96</v>
       </c>
       <c r="R111">
-        <v>94.7</v>
+        <v>93.7</v>
       </c>
       <c r="S111">
         <v>100</v>
       </c>
       <c r="T111">
-        <v>-5.3</v>
+        <v>-6.3</v>
       </c>
       <c r="U111">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="V111">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="W111">
-        <v>88.33</v>
+        <v>93.33</v>
       </c>
       <c r="X111">
-        <v>90.33</v>
+        <v>93.33</v>
       </c>
       <c r="Y111" t="str">
         <v/>
@@ -8996,55 +8996,55 @@
         <v>800</v>
       </c>
       <c r="H112">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I112">
         <v>81</v>
       </c>
       <c r="J112">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K112">
         <v>0</v>
       </c>
       <c r="L112">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="M112">
-        <v>478</v>
+        <v>457</v>
       </c>
       <c r="N112">
-        <v>470</v>
+        <v>450</v>
       </c>
       <c r="O112">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P112">
         <v>0</v>
       </c>
       <c r="Q112">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="R112">
-        <v>59.75</v>
+        <v>57.13</v>
       </c>
       <c r="S112">
         <v>100</v>
       </c>
       <c r="T112">
-        <v>-40.25</v>
+        <v>-42.87</v>
       </c>
       <c r="U112">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="V112">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W112">
-        <v>95</v>
+        <v>98.33</v>
       </c>
       <c r="X112">
-        <v>61.67</v>
+        <v>61.17</v>
       </c>
       <c r="Y112" t="str">
         <v/>
@@ -9073,55 +9073,55 @@
         <v>750</v>
       </c>
       <c r="H113">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="I113">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="J113">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K113">
         <v>0</v>
       </c>
       <c r="L113">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="M113">
-        <v>695</v>
+        <v>706</v>
       </c>
       <c r="N113">
-        <v>686</v>
+        <v>700</v>
       </c>
       <c r="O113">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="P113">
         <v>0</v>
       </c>
       <c r="Q113">
-        <v>1.29</v>
+        <v>0.85</v>
       </c>
       <c r="R113">
-        <v>92.67</v>
+        <v>94.13</v>
       </c>
       <c r="S113">
         <v>100</v>
       </c>
       <c r="T113">
-        <v>-7.33</v>
+        <v>-5.87</v>
       </c>
       <c r="U113">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="V113">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W113">
-        <v>98.33</v>
+        <v>100</v>
       </c>
       <c r="X113">
-        <v>94.67</v>
+        <v>93.33</v>
       </c>
       <c r="Y113" t="str">
         <v/>
@@ -9150,55 +9150,55 @@
         <v>600</v>
       </c>
       <c r="H114">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="I114">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="J114">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K114">
         <v>0</v>
       </c>
       <c r="L114">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M114">
-        <v>572</v>
+        <v>594</v>
       </c>
       <c r="N114">
-        <v>566</v>
+        <v>583</v>
       </c>
       <c r="O114">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="P114">
         <v>0</v>
       </c>
       <c r="Q114">
-        <v>1.05</v>
+        <v>1.85</v>
       </c>
       <c r="R114">
-        <v>95.33</v>
+        <v>99</v>
       </c>
       <c r="S114">
         <v>100</v>
       </c>
       <c r="T114">
-        <v>-4.67</v>
+        <v>-1</v>
       </c>
       <c r="U114">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="V114">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="W114">
-        <v>98.33</v>
+        <v>91.67</v>
       </c>
       <c r="X114">
-        <v>92.83</v>
+        <v>89.33</v>
       </c>
       <c r="Y114" t="str">
         <v/>
@@ -9227,10 +9227,10 @@
         <v>550</v>
       </c>
       <c r="H115">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I115">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="J115">
         <v>0</v>
@@ -9242,40 +9242,40 @@
         <v>0</v>
       </c>
       <c r="M115">
-        <v>493</v>
+        <v>511</v>
       </c>
       <c r="N115">
-        <v>482</v>
+        <v>501</v>
       </c>
       <c r="O115">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P115">
         <v>0</v>
       </c>
       <c r="Q115">
-        <v>2.23</v>
+        <v>1.96</v>
       </c>
       <c r="R115">
-        <v>89.64</v>
+        <v>92.91</v>
       </c>
       <c r="S115">
         <v>100</v>
       </c>
       <c r="T115">
-        <v>-10.36</v>
+        <v>-7.09</v>
       </c>
       <c r="U115">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="V115">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W115">
-        <v>93.33</v>
+        <v>95</v>
       </c>
       <c r="X115">
-        <v>88.17</v>
+        <v>90.83</v>
       </c>
       <c r="Y115" t="str">
         <v/>
@@ -9304,55 +9304,55 @@
         <v>900</v>
       </c>
       <c r="H116">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="I116">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="J116">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K116">
         <v>0</v>
       </c>
       <c r="L116">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M116">
-        <v>864</v>
+        <v>855</v>
       </c>
       <c r="N116">
-        <v>798</v>
+        <v>780</v>
       </c>
       <c r="O116">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="P116">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q116">
-        <v>6.13</v>
+        <v>7.13</v>
       </c>
       <c r="R116">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S116">
         <v>100</v>
       </c>
       <c r="T116">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="U116">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="V116">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="W116">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="X116">
-        <v>89.83</v>
+        <v>90</v>
       </c>
       <c r="Y116" t="str">
         <v/>
@@ -9381,55 +9381,55 @@
         <v>1500</v>
       </c>
       <c r="H117">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="I117">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="J117">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K117">
         <v>0</v>
       </c>
       <c r="L117">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="M117">
-        <v>1231</v>
+        <v>1163</v>
       </c>
       <c r="N117">
-        <v>1190</v>
+        <v>1127</v>
       </c>
       <c r="O117">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="P117">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q117">
-        <v>2.44</v>
+        <v>2.24</v>
       </c>
       <c r="R117">
-        <v>82.07</v>
+        <v>77.53</v>
       </c>
       <c r="S117">
         <v>100</v>
       </c>
       <c r="T117">
-        <v>-17.93</v>
+        <v>-22.47</v>
       </c>
       <c r="U117">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="V117">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W117">
-        <v>86.67</v>
+        <v>100</v>
       </c>
       <c r="X117">
-        <v>83.67</v>
+        <v>85</v>
       </c>
       <c r="Y117" t="str">
         <v/>
@@ -9458,10 +9458,10 @@
         <v>1400</v>
       </c>
       <c r="H118">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="I118">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="J118">
         <v>1</v>
@@ -9470,43 +9470,43 @@
         <v>0</v>
       </c>
       <c r="L118">
-        <v>0.81</v>
+        <v>0.78</v>
       </c>
       <c r="M118">
-        <v>1345</v>
+        <v>1283</v>
       </c>
       <c r="N118">
-        <v>1336</v>
+        <v>1271</v>
       </c>
       <c r="O118">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="P118">
         <v>0</v>
       </c>
       <c r="Q118">
-        <v>0.67</v>
+        <v>0.94</v>
       </c>
       <c r="R118">
-        <v>96.07</v>
+        <v>91.64</v>
       </c>
       <c r="S118">
         <v>100</v>
       </c>
       <c r="T118">
-        <v>-3.93</v>
+        <v>-8.36</v>
       </c>
       <c r="U118">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="V118">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W118">
-        <v>91.67</v>
+        <v>100</v>
       </c>
       <c r="X118">
-        <v>92.5</v>
+        <v>92.17</v>
       </c>
       <c r="Y118" t="str">
         <v/>
@@ -9550,40 +9550,40 @@
         <v>2.17</v>
       </c>
       <c r="M119">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="N119">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="O119">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P119">
         <v>0</v>
       </c>
       <c r="Q119">
-        <v>1.15</v>
+        <v>0.94</v>
       </c>
       <c r="R119">
-        <v>96.22</v>
+        <v>94.67</v>
       </c>
       <c r="S119">
         <v>100</v>
       </c>
       <c r="T119">
-        <v>-3.78</v>
+        <v>-5.33</v>
       </c>
       <c r="U119">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="V119">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W119">
-        <v>100</v>
+        <v>86.67</v>
       </c>
       <c r="X119">
-        <v>91.17</v>
+        <v>91.83</v>
       </c>
       <c r="Y119" t="str">
         <v/>
@@ -9612,10 +9612,10 @@
         <v>400</v>
       </c>
       <c r="H120">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="I120">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="J120">
         <v>0</v>
@@ -9627,40 +9627,40 @@
         <v>0</v>
       </c>
       <c r="M120">
-        <v>321</v>
+        <v>335</v>
       </c>
       <c r="N120">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="O120">
         <v>4</v>
       </c>
       <c r="P120">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q120">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="R120">
-        <v>80.25</v>
+        <v>83.75</v>
       </c>
       <c r="S120">
         <v>100</v>
       </c>
       <c r="T120">
-        <v>-19.75</v>
+        <v>-16.25</v>
       </c>
       <c r="U120">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V120">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W120">
-        <v>98.33</v>
+        <v>95</v>
       </c>
       <c r="X120">
-        <v>89</v>
+        <v>89.17</v>
       </c>
       <c r="Y120" t="str">
         <v/>
@@ -9689,52 +9689,52 @@
         <v>2000</v>
       </c>
       <c r="H121">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="I121">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="J121">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K121">
         <v>0</v>
       </c>
       <c r="L121">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="M121">
-        <v>1885</v>
+        <v>1916</v>
       </c>
       <c r="N121">
-        <v>1883</v>
+        <v>1908</v>
       </c>
       <c r="O121">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="P121">
         <v>0</v>
       </c>
       <c r="Q121">
-        <v>0.11</v>
+        <v>0.42</v>
       </c>
       <c r="R121">
-        <v>94.25</v>
+        <v>95.8</v>
       </c>
       <c r="S121">
         <v>100</v>
       </c>
       <c r="T121">
-        <v>-5.75</v>
+        <v>-4.2</v>
       </c>
       <c r="U121">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="V121">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W121">
-        <v>90</v>
+        <v>91.67</v>
       </c>
       <c r="X121">
         <v>89.67</v>
